--- a/data/חכמי_ישראל.xlsx
+++ b/data/חכמי_ישראל.xlsx
@@ -361,7 +361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L554"/>
+  <dimension ref="A1:L598"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="3" min="1" max="1"/>
@@ -34071,6 +34071,1978 @@
         </is>
       </c>
     </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>אבנימוס הגרדי (אוינומאוס מגדרה)</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>90–160</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>ארץ ישראל</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>תנאים</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>פילוסופיה</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr"/>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>פילוסוף ציני מגדרה שחז"ל ראו בו את 'גדול פילוסופי אומות העולם'. בן שיחם של חכמים ובעל פולמוס חריף נגד האמונה בגורל.</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr"/>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>אברהם אבינו</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>1812–1637 לפנה״ס</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>חברון</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>האבות</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>אמונה, חסד</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr"/>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>אבי האומה. יצא מאור כשדים בקריאת 'לך לך', הפיץ את האמונה בא-ל אחד וכרת את ברית בין הבתרים.</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr"/>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>556</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>ברוריה</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>110–170</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>טבריה</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>תנאים</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>תורה שבעל פה</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>נשים</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>החכמה הנודעת שבדור התנאים, אשת רבי מאיר ובת רבי חנינא בן תרדיון. הלכותיה ולמדנותה מובאות בש"ס — 'תלת מאה שמעתתא ביומא'.</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr"/>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>דוד המלך</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>1040–970 לפנה״ס</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>ירושלים</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>המלכים</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>מלכות, תהילים</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr"/>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>מייסד מלכות בית דוד ומחבר ספר תהילים. כבש את ירושלים והעלה אליה את ארון הברית — 'נעים זמירות ישראל'.</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr"/>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>הבעל שם טוב (רבי ישראל בעש"ט)</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>1698–1760</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>אוקראינה</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>חסידות, קבלה</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr"/>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>מייסד תנועת החסידות. לימד שאין מקום פנוי ממנו, העמיד את הדבקות, השמחה ואהבת כל יהודי במרכז העבודה — ושינה את פני יהדות מזרח אירופה.</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>לית אתר פנוי מיניה — עבודת ה' בדבקות ובשמחה</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>הגאון מווילנא (הגר"א)</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>1720–1797</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>וילנה</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>תלמוד, הלכה, קבלה, דקדוק</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr"/>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>גאון הדורות בליטא. שקד על התורה בהתמדה מופלאה, הקיף נגלה ונסתר, דקדוק ומתמטיקה, והעמיד את לימוד התורה בעיון מדויק במרכז — אבי עולם הישיבות הליטאי.</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>עמל התורה בדיוק ובבקיאות — נגלה ונסתר כאחד</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>הרב אברהם יצחקי (זרע אברהם)</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>1661–1729</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>ירושלים</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>הלכה, הנהגה</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr"/>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>הראשון לציון ומחבר שו"ת 'זרע אברהם'. ממנהיגי ירושלים במאבק בשבתאות ובביצור מעמדה התורני של העיר.</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr"/>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>561</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>הרב אברהם מרדכי יצחקי (הרב מפורת)</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr"/>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>מושב פורת, השרון</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>קבלה, הנהגת קהילה</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr"/>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>רב פעיל בישראל המשלב מסורת קבלית עם הנגשה דיגיטלית של תורת הנסתר. עומד בראש בית המדרש 'דוד המלך' במושב פורת, מוקד ללימוד זוהר והתבודדות.</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>הנגשת הקבלה ככלי מעשי לתיקון הנפש בעידן הדיגיטלי.</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>הרב אהרן קוטלר</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>1891–1962</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>ארה"ב</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>ראשות ישיבה</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr"/>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>מייסד ישיבת לייקווד ואדריכל עולם התורה באמריקה שלאחר השואה. העמיד את לימוד התורה לשמה כערך עליון ללא פשרות.</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr"/>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>563</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>הרב יוסף יצחק שניאורסון (הריי"צ)</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>1880–1950</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>ארה"ב</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>חסידות, הנהגה</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr"/>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>האדמו"ר השישי של חב"ד. עמד בעוז מול השלטון הסובייטי, שוחרר ממאסר מוות, והעביר את מרכז חב"ד לאמריקה.</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr"/>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>הרב לורד יונתן זקס</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>1948–2020</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>אנגליה</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>הגות, הנהגה</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr"/>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>רבה הראשי של בריטניה והוגה יהודי בעל השפעה עולמית. הציג את קול התורה בשפת הפילוסופיה והמוסר האוניברסלי.</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>הרב מרדכי עטיה</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>1883–1978</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>ירושלים</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>קבלה</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr"/>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>מקובל וראש ישיבת המקובלים, מחכמי ארם צובא שקבעו משכנם בירושלים. קרא לגאולה מתוך תורת הסוד ומעשה.</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr"/>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>הרב משה צוריאל</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>1938–2023</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>בני ברק</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>מוסר, מחשבה, קבלה</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr"/>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>משגיח ישיבת 'שעלבים' ומחבר פורה. כינס וביאר את כתבי הראי"ה קוק, הגר"א והרמח"ל — גשר בין עולם המוסר לתורת ארץ ישראל.</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr"/>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>הרב שלמה קרליבך</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>1925–1994</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>ארה"ב</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>נגינה, קירוב</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr"/>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>'הרבי המרקד' — מחולל מהפכת הנגינה היהודית בדור התשובה. ניגוניו ופתיחת לבו קירבו רבבות ליהדות.</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr"/>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>יהודית</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>170–100 לפנה״ס</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>ארץ ישראל</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>גבורה</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>נשים</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>גיבורת הספר החיצוני הקרוי על שמה, שמסרה נפשה להצלת עמה. דמותה נקשרה במסורת לנס חנוכה.</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr"/>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>569</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>יוסל מרוסהיים</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>1476–1554</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>אשכנז</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>שתדלנות, הנהגה</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr"/>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>השתדלן הגדול של יהדות אשכנז מול הקיסר קרל החמישי. 'ספר המקנה' שלו — עדות אישית להנהגה בדור של גזרות ורפורמציה.</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr"/>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>יעקב אבינו</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>1652–1505 לפנה״ס</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>חברון</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>האבות</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>תורה, אמת</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr"/>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>בחיר האבות ואבי שנים־עשר השבטים. 'איש תם יושב אוהלים' שירד למצרים והניח את יסוד בית ישראל.</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr"/>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>יצחק אבינו</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>1712–1532 לפנה״ס</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>חברון</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>האבות</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>גבורה, תפילה</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr"/>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>השני שבאבות. נעקד על גבי המזבח בהר המוריה, וחפר מחדש את בארות אביו — ממשיך הדרך בארץ.</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr"/>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>ישעיהו הנביא</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>765–695 לפנה״ס</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>ירושלים</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>המלכים</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>נבואה</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr"/>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>מגדולי נביאי הכתב. נבואות החורבן והנחמה שלו — 'נחמו נחמו עמי' — מלוות את ישראל בכל הדורות.</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr"/>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>מהר"י בירב (רבי יעקב בירב)</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>1474–1546</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>צפת</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>הלכה</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr"/>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>גדול חכמי צפת בדורו ויוזם חידוש הסמיכה (1538) כצעד לקירוב הגאולה — מהלך שהצית את הפולמוס הגדול עם חכמי ירושלים.</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr"/>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>משה רבנו</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>1391–1271 לפנה״ס</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>מצרים</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>יציאת מצרים</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>תורה, נבואה, הנהגה</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr"/>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>אדון הנביאים ומקבל התורה בסיני. הוציא את ישראל ממצרים, קיבל את הלוחות ומסר תורה לכל ישראל — ראש שלשלת הקבלה.</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>משה קיבל תורה מסיני ומסרה ליהושע (אבות א, א)</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>עזרא הסופר</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>480–420 לפנה״ס</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>ירושלים</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>תורה, הנהגה</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr"/>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>מחדש התורה בישראל בראשית ימי הבית השני. העלה את הגולה מבבל, כונן את קריאת התורה ברבים — 'ראוי היה עזרא שתינתן תורה על ידו'.</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr"/>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>רב הונא</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>216–296</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>סורא</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>אמוראים</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>הלכה</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr"/>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>עמוד התווך של הדור השני לאמוראי בבל וראש ישיבת סורא ארבעים שנה. הלכה כמותו בממונות ברוב מחלוקותיו.</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr"/>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>577</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>רבי אבון הגדול</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>900–960</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>מגנצא</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>גאונים</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>תורה, פיוט</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr"/>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>מאבות הקהילה הרבנית הקדומה ברינוס. ממניחי היסוד לתרבות התורה של אשכנז הקדומה, דורות לפני רבנו גרשום.</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr"/>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>רבי טרפון</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>46–117</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>יבנה</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>תנאים</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>הלכה</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr"/>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>מגדולי תנאי יבנה, כהן שזכה לשרת במקדש. בר פלוגתא ואוהבו של רבי עקיבא; 'היום קצר והמלאכה מרובה'.</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr"/>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>רבי יהודה הלוי (ריה"ל)</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>1075–1141</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>טולדו</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>ראשונים</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>שירה, הגות</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr"/>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>מגדולי משוררי ספרד והוגה 'הכוזרי'. שירת געגועיו לציון — 'לבי במזרח ואנוכי בסוף מערב' — מלווה את האומה; בסוף ימיו יצא לארץ ישראל.</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr"/>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>רבי יהודה הנשיא</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>135–217</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>ציפורי</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>תנאים</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>משנה, הנהגה</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr"/>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>עורך המשנה וחותם תקופת התנאים. איחד את מסורות התורה שבעל פה לחיבור אחד מוסמך, ושילב גדולה בתורה עם עושר ומנהיגות מול רומא.</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>עריכת המשנה — חתימת התורה שבעל פה הראשונה</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>581</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>רבי יעקב הכהן (המקובל)</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>1200–1270</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>קאסטיליה</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>ראשונים</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>קבלה</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr"/>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>ממקובלי קאסטיליה הראשונים, מאבות 'קבלת האחים הכהנים'. חיבוריו על האותיות והמרכבה קדמו לזוהר והשפיעו עליו.</t>
+        </is>
+      </c>
+      <c r="J582" t="inlineStr"/>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>רבי יצחק אלפסי (הרי"ף)</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>1013–1103</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>פאס</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>ראשונים</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>הלכה</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr"/>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>גדול פוסקי הדור שבין הגאונים לראשונים. 'הלכות הרי"ף' זיקקו את התלמוד לפסק הלכה ושימשו עמוד יסוד לשולחן ערוך.</t>
+        </is>
+      </c>
+      <c r="J583" t="inlineStr"/>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>רבי יצחק הלוי (סגן לויה)</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>1000–1080</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>וורמייזא</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>ראשונים</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>תלמוד, פרשנות</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr"/>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>מראשי ישיבות לותיר ורבותיו המובהקים של רש"י בוורמייזא. ממעצבי מסורת הלימוד האשכנזית הקדומה.</t>
+        </is>
+      </c>
+      <c r="J584" t="inlineStr"/>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>רבי ישמעאל (בן אלישע)</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>60–135</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>ארץ ישראל</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>תנאים</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>מדרש הלכה</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr"/>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>אב עולם ובעל שלוש-עשרה המידות שהתורה נדרשת בהן. בר פלוגתא הגדול של רבי עקיבא בדרכי המדרש — 'דיברה תורה כלשון בני אדם'.</t>
+        </is>
+      </c>
+      <c r="J585" t="inlineStr"/>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>585</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>רבי לוי בן חביב (המהרלב"ח)</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>1483–1545</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>ירושלים</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>הלכה</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr"/>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>רבה של ירושלים והמתנגד הגדול לחידוש הסמיכה. 'קונטרס הסמיכה' שלו הכריע את הפולמוס ההלכתי הנודע מול חכמי צפת.</t>
+        </is>
+      </c>
+      <c r="J586" t="inlineStr"/>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>רבי משה אלשקר (מהר"ם אלשקר)</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>1466–1542</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>מצרים</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>הלכה</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr"/>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>מגדולי הפוסקים שאחרי גירוש ספרד. ניצל מספינה טובעת, כיהן בדיינות במצרים ועלה בסוף ימיו לירושלים.</t>
+        </is>
+      </c>
+      <c r="J587" t="inlineStr"/>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>רבי משה חיים אפרים מסדילקוב</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>1748–1800</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>אוקראינה</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>חסידות</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr"/>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>נכד הבעל שם טוב ובעל 'דגל מחנה אפרים' — מן המקורות הראשונים והנאמנים לתורת הסבא הגדול.</t>
+        </is>
+      </c>
+      <c r="J588" t="inlineStr"/>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>רבי משה מקוצי (הסמ"ג)</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>1200–1260</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>צרפת</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>ראשונים</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>הלכה, דרשנות</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr"/>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>מבעלי התוספות ומחבר 'ספר מצוות גדול' — הקודקס ההלכתי הגדול של יהדות צרפת. סבב בקהילות ספרד ואשכנז כמוכיח ומעורר.</t>
+        </is>
+      </c>
+      <c r="J589" t="inlineStr"/>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>רבי נתן מברסלב (מנמירוב)</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>1780–1844</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>אוקראינה</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>חסידות</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr"/>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>תלמידו הגדול וסופרו של רבי נחמן מברסלב. העלה על הכתב את תורותיו, ייסד את מסורת ההתבודדות והתפילה — 'ליקוטי תפילות'.</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr"/>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>רבי רפאל ברוך טולידאנו</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>1890–1971</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>מקנס</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>הלכה, פיוט</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr"/>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>ראב"ד מקנס ומחבר 'קיצור שולחן ערוך' לבני ספרד. פיוטו 'אשתחווה אפיים ארצה' מושר בכל תפוצות המזרח.</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr"/>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>591</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>רבן גמליאל דיבנה</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>50–118</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>יבנה</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>תנאים</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>הנהגה, הלכה</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr"/>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>נשיא ישראל אחרי החורבן. ביצר את סמכות הנשיאות ואת אחדות ההלכה בדור השיקום של יבנה.</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr"/>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>רבן יוחנן בן זכאי</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>10 לפנה״ס–74</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>יבנה</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>תנאים</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>תורה שבעל פה, הנהגה</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr"/>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>מציל התורה בדור החורבן. יצא מירושלים הנצורה וביקש 'תן לי יבנה וחכמיה' — ובכך הבטיח את המשך התורה שבעל פה אחרי חורבן הבית.</t>
+        </is>
+      </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>תן לי יבנה וחכמיה</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>רבקה אמנו</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>1677–1556 לפנה״ס</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>חברון</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>האבות</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>אמהות האומה</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>נשים</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>השנייה שבאמהות. ראתה ברוח קודשה את ייעודם של בניה והכריעה את המשך דרך הברית — 'ורב יעבוד צעיר'.</t>
+        </is>
+      </c>
+      <c r="J594" t="inlineStr"/>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>רש"י (רבי שלמה יצחקי)</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>1040–1105</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>טרואה</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>ראשונים</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>פרשנות המקרא, פרשנות התלמוד</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr"/>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>גדול פרשני ישראל. פירושו לתורה ולתלמוד — בהיר, תמציתי וצמוד לפשט — פתח את שערי הלימוד לכל הדורות, ובלעדיו אין דף גמרא נלמד.</t>
+        </is>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>פשוטו של מקרא — פירוש שכל תלמיד יכול להיכנס בו</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>שלמה המלך</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>1010–931 לפנה״ס</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>ירושלים</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>המלכים</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>חכמה, מלכות</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr"/>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>החכם מכל אדם ובונה בית המקדש הראשון. חיבר את משלי, קהלת ושיר השירים.</t>
+        </is>
+      </c>
+      <c r="J596" t="inlineStr"/>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>שמואל הנביא</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>1120–1012 לפנה״ס</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>ארץ ישראל</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>השופטים</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>נבואה, הנהגה</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr"/>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>אחרון השופטים וגדול הנביאים אחרי משה. הקים את המלוכה בישראל ומשח את שאול ואת דוד.</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr"/>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>שמואל הנגיד</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>993–1056</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>גרנדה</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>ראשונים</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>הלכה, שירה, מדינאות</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr"/>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>וזיר גרנדה, מצביא, משורר ופוסק — סמל תור הזהב בספרד. 'מבוא התלמוד' שלו נלמד עד היום.</t>
+        </is>
+      </c>
+      <c r="J598" t="inlineStr"/>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/חכמי_ישראל.xlsx
+++ b/data/חכמי_ישראל.xlsx
@@ -361,7 +361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L598"/>
+  <dimension ref="A1:L612"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="3" min="1" max="1"/>
@@ -33244,7 +33244,7 @@
       </c>
       <c r="F540" s="3" t="inlineStr">
         <is>
-          <t>העת החדשה</t>
+          <t>אחרונים</t>
         </is>
       </c>
       <c r="G540" s="3" t="inlineStr">
@@ -34072,1976 +34072,2788 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" t="inlineStr">
+      <c r="A555" s="3" t="inlineStr">
         <is>
           <t>554</t>
         </is>
       </c>
-      <c r="B555" t="inlineStr">
+      <c r="B555" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C555" t="inlineStr">
+      <c r="C555" s="3" t="inlineStr">
         <is>
           <t>אבנימוס הגרדי (אוינומאוס מגדרה)</t>
         </is>
       </c>
-      <c r="D555" t="inlineStr">
+      <c r="D555" s="3" t="inlineStr">
         <is>
           <t>90–160</t>
         </is>
       </c>
-      <c r="E555" t="inlineStr">
+      <c r="E555" s="3" t="inlineStr">
         <is>
           <t>ארץ ישראל</t>
         </is>
       </c>
-      <c r="F555" t="inlineStr">
+      <c r="F555" s="3" t="inlineStr">
         <is>
           <t>תנאים</t>
         </is>
       </c>
-      <c r="G555" t="inlineStr">
+      <c r="G555" s="3" t="inlineStr">
         <is>
           <t>פילוסופיה</t>
         </is>
       </c>
-      <c r="H555" t="inlineStr"/>
-      <c r="I555" t="inlineStr">
+      <c r="H555" s="3" t="inlineStr"/>
+      <c r="I555" s="3" t="inlineStr">
         <is>
           <t>פילוסוף ציני מגדרה שחז"ל ראו בו את 'גדול פילוסופי אומות העולם'. בן שיחם של חכמים ובעל פולמוס חריף נגד האמונה בגורל.</t>
         </is>
       </c>
-      <c r="J555" t="inlineStr"/>
+      <c r="J555" s="3" t="inlineStr"/>
     </row>
     <row r="556">
-      <c r="A556" t="inlineStr">
+      <c r="A556" s="3" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="B556" t="inlineStr">
+      <c r="B556" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C556" t="inlineStr">
+      <c r="C556" s="3" t="inlineStr">
         <is>
           <t>אברהם אבינו</t>
         </is>
       </c>
-      <c r="D556" t="inlineStr">
+      <c r="D556" s="3" t="inlineStr">
         <is>
           <t>1812–1637 לפנה״ס</t>
         </is>
       </c>
-      <c r="E556" t="inlineStr">
+      <c r="E556" s="3" t="inlineStr">
         <is>
           <t>חברון</t>
         </is>
       </c>
-      <c r="F556" t="inlineStr">
+      <c r="F556" s="3" t="inlineStr">
         <is>
           <t>האבות</t>
         </is>
       </c>
-      <c r="G556" t="inlineStr">
+      <c r="G556" s="3" t="inlineStr">
         <is>
           <t>אמונה, חסד</t>
         </is>
       </c>
-      <c r="H556" t="inlineStr"/>
-      <c r="I556" t="inlineStr">
+      <c r="H556" s="3" t="inlineStr"/>
+      <c r="I556" s="3" t="inlineStr">
         <is>
           <t>אבי האומה. יצא מאור כשדים בקריאת 'לך לך', הפיץ את האמונה בא-ל אחד וכרת את ברית בין הבתרים.</t>
         </is>
       </c>
-      <c r="J556" t="inlineStr"/>
+      <c r="J556" s="3" t="inlineStr"/>
     </row>
     <row r="557">
-      <c r="A557" t="inlineStr">
+      <c r="A557" s="3" t="inlineStr">
         <is>
           <t>556</t>
         </is>
       </c>
-      <c r="B557" t="inlineStr">
+      <c r="B557" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C557" t="inlineStr">
+      <c r="C557" s="3" t="inlineStr">
         <is>
           <t>ברוריה</t>
         </is>
       </c>
-      <c r="D557" t="inlineStr">
+      <c r="D557" s="3" t="inlineStr">
         <is>
           <t>110–170</t>
         </is>
       </c>
-      <c r="E557" t="inlineStr">
+      <c r="E557" s="3" t="inlineStr">
         <is>
           <t>טבריה</t>
         </is>
       </c>
-      <c r="F557" t="inlineStr">
+      <c r="F557" s="3" t="inlineStr">
         <is>
           <t>תנאים</t>
         </is>
       </c>
-      <c r="G557" t="inlineStr">
+      <c r="G557" s="3" t="inlineStr">
         <is>
           <t>תורה שבעל פה</t>
         </is>
       </c>
-      <c r="H557" t="inlineStr">
+      <c r="H557" s="3" t="inlineStr">
         <is>
           <t>נשים</t>
         </is>
       </c>
-      <c r="I557" t="inlineStr">
+      <c r="I557" s="3" t="inlineStr">
         <is>
           <t>החכמה הנודעת שבדור התנאים, אשת רבי מאיר ובת רבי חנינא בן תרדיון. הלכותיה ולמדנותה מובאות בש"ס — 'תלת מאה שמעתתא ביומא'.</t>
         </is>
       </c>
-      <c r="J557" t="inlineStr"/>
+      <c r="J557" s="3" t="inlineStr"/>
     </row>
     <row r="558">
-      <c r="A558" t="inlineStr">
+      <c r="A558" s="3" t="inlineStr">
         <is>
           <t>557</t>
         </is>
       </c>
-      <c r="B558" t="inlineStr">
+      <c r="B558" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C558" t="inlineStr">
+      <c r="C558" s="3" t="inlineStr">
         <is>
           <t>דוד המלך</t>
         </is>
       </c>
-      <c r="D558" t="inlineStr">
+      <c r="D558" s="3" t="inlineStr">
         <is>
           <t>1040–970 לפנה״ס</t>
         </is>
       </c>
-      <c r="E558" t="inlineStr">
+      <c r="E558" s="3" t="inlineStr">
         <is>
           <t>ירושלים</t>
         </is>
       </c>
-      <c r="F558" t="inlineStr">
+      <c r="F558" s="3" t="inlineStr">
         <is>
           <t>המלכים</t>
         </is>
       </c>
-      <c r="G558" t="inlineStr">
+      <c r="G558" s="3" t="inlineStr">
         <is>
           <t>מלכות, תהילים</t>
         </is>
       </c>
-      <c r="H558" t="inlineStr"/>
-      <c r="I558" t="inlineStr">
+      <c r="H558" s="3" t="inlineStr"/>
+      <c r="I558" s="3" t="inlineStr">
         <is>
           <t>מייסד מלכות בית דוד ומחבר ספר תהילים. כבש את ירושלים והעלה אליה את ארון הברית — 'נעים זמירות ישראל'.</t>
         </is>
       </c>
-      <c r="J558" t="inlineStr"/>
+      <c r="J558" s="3" t="inlineStr"/>
     </row>
     <row r="559">
-      <c r="A559" t="inlineStr">
+      <c r="A559" s="3" t="inlineStr">
         <is>
           <t>558</t>
         </is>
       </c>
-      <c r="B559" t="inlineStr">
+      <c r="B559" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C559" t="inlineStr">
+      <c r="C559" s="3" t="inlineStr">
         <is>
           <t>הבעל שם טוב (רבי ישראל בעש"ט)</t>
         </is>
       </c>
-      <c r="D559" t="inlineStr">
+      <c r="D559" s="3" t="inlineStr">
         <is>
           <t>1698–1760</t>
         </is>
       </c>
-      <c r="E559" t="inlineStr">
+      <c r="E559" s="3" t="inlineStr">
         <is>
           <t>אוקראינה</t>
         </is>
       </c>
-      <c r="F559" t="inlineStr">
+      <c r="F559" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G559" t="inlineStr">
+      <c r="G559" s="3" t="inlineStr">
         <is>
           <t>חסידות, קבלה</t>
         </is>
       </c>
-      <c r="H559" t="inlineStr"/>
-      <c r="I559" t="inlineStr">
+      <c r="H559" s="3" t="inlineStr"/>
+      <c r="I559" s="3" t="inlineStr">
         <is>
           <t>מייסד תנועת החסידות. לימד שאין מקום פנוי ממנו, העמיד את הדבקות, השמחה ואהבת כל יהודי במרכז העבודה — ושינה את פני יהדות מזרח אירופה.</t>
         </is>
       </c>
-      <c r="J559" t="inlineStr">
+      <c r="J559" s="3" t="inlineStr">
         <is>
           <t>לית אתר פנוי מיניה — עבודת ה' בדבקות ובשמחה</t>
         </is>
       </c>
     </row>
     <row r="560">
-      <c r="A560" t="inlineStr">
+      <c r="A560" s="3" t="inlineStr">
         <is>
           <t>559</t>
         </is>
       </c>
-      <c r="B560" t="inlineStr">
+      <c r="B560" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C560" t="inlineStr">
+      <c r="C560" s="3" t="inlineStr">
         <is>
           <t>הגאון מווילנא (הגר"א)</t>
         </is>
       </c>
-      <c r="D560" t="inlineStr">
+      <c r="D560" s="3" t="inlineStr">
         <is>
           <t>1720–1797</t>
         </is>
       </c>
-      <c r="E560" t="inlineStr">
+      <c r="E560" s="3" t="inlineStr">
         <is>
           <t>וילנה</t>
         </is>
       </c>
-      <c r="F560" t="inlineStr">
+      <c r="F560" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G560" t="inlineStr">
+      <c r="G560" s="3" t="inlineStr">
         <is>
           <t>תלמוד, הלכה, קבלה, דקדוק</t>
         </is>
       </c>
-      <c r="H560" t="inlineStr"/>
-      <c r="I560" t="inlineStr">
+      <c r="H560" s="3" t="inlineStr"/>
+      <c r="I560" s="3" t="inlineStr">
         <is>
           <t>גאון הדורות בליטא. שקד על התורה בהתמדה מופלאה, הקיף נגלה ונסתר, דקדוק ומתמטיקה, והעמיד את לימוד התורה בעיון מדויק במרכז — אבי עולם הישיבות הליטאי.</t>
         </is>
       </c>
-      <c r="J560" t="inlineStr">
+      <c r="J560" s="3" t="inlineStr">
         <is>
           <t>עמל התורה בדיוק ובבקיאות — נגלה ונסתר כאחד</t>
         </is>
       </c>
     </row>
     <row r="561">
-      <c r="A561" t="inlineStr">
+      <c r="A561" s="3" t="inlineStr">
         <is>
           <t>560</t>
         </is>
       </c>
-      <c r="B561" t="inlineStr">
+      <c r="B561" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C561" t="inlineStr">
+      <c r="C561" s="3" t="inlineStr">
         <is>
           <t>הרב אברהם יצחקי (זרע אברהם)</t>
         </is>
       </c>
-      <c r="D561" t="inlineStr">
+      <c r="D561" s="3" t="inlineStr">
         <is>
           <t>1661–1729</t>
         </is>
       </c>
-      <c r="E561" t="inlineStr">
+      <c r="E561" s="3" t="inlineStr">
         <is>
           <t>ירושלים</t>
         </is>
       </c>
-      <c r="F561" t="inlineStr">
+      <c r="F561" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G561" t="inlineStr">
+      <c r="G561" s="3" t="inlineStr">
         <is>
           <t>הלכה, הנהגה</t>
         </is>
       </c>
-      <c r="H561" t="inlineStr"/>
-      <c r="I561" t="inlineStr">
+      <c r="H561" s="3" t="inlineStr"/>
+      <c r="I561" s="3" t="inlineStr">
         <is>
           <t>הראשון לציון ומחבר שו"ת 'זרע אברהם'. ממנהיגי ירושלים במאבק בשבתאות ובביצור מעמדה התורני של העיר.</t>
         </is>
       </c>
-      <c r="J561" t="inlineStr"/>
+      <c r="J561" s="3" t="inlineStr"/>
     </row>
     <row r="562">
-      <c r="A562" t="inlineStr">
+      <c r="A562" s="3" t="inlineStr">
         <is>
           <t>561</t>
         </is>
       </c>
-      <c r="B562" t="inlineStr">
+      <c r="B562" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C562" t="inlineStr">
+      <c r="C562" s="3" t="inlineStr">
         <is>
           <t>הרב אברהם מרדכי יצחקי (הרב מפורת)</t>
         </is>
       </c>
-      <c r="D562" t="inlineStr"/>
-      <c r="E562" t="inlineStr">
+      <c r="D562" s="3" t="inlineStr"/>
+      <c r="E562" s="3" t="inlineStr">
         <is>
           <t>מושב פורת, השרון</t>
         </is>
       </c>
-      <c r="F562" t="inlineStr">
+      <c r="F562" s="3" t="inlineStr">
         <is>
           <t>מודרני</t>
         </is>
       </c>
-      <c r="G562" t="inlineStr">
+      <c r="G562" s="3" t="inlineStr">
         <is>
           <t>קבלה, הנהגת קהילה</t>
         </is>
       </c>
-      <c r="H562" t="inlineStr"/>
-      <c r="I562" t="inlineStr">
+      <c r="H562" s="3" t="inlineStr"/>
+      <c r="I562" s="3" t="inlineStr">
         <is>
           <t>רב פעיל בישראל המשלב מסורת קבלית עם הנגשה דיגיטלית של תורת הנסתר. עומד בראש בית המדרש 'דוד המלך' במושב פורת, מוקד ללימוד זוהר והתבודדות.</t>
         </is>
       </c>
-      <c r="J562" t="inlineStr">
+      <c r="J562" s="3" t="inlineStr">
         <is>
           <t>הנגשת הקבלה ככלי מעשי לתיקון הנפש בעידן הדיגיטלי.</t>
         </is>
       </c>
     </row>
     <row r="563">
-      <c r="A563" t="inlineStr">
+      <c r="A563" s="3" t="inlineStr">
         <is>
           <t>562</t>
         </is>
       </c>
-      <c r="B563" t="inlineStr">
+      <c r="B563" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C563" t="inlineStr">
+      <c r="C563" s="3" t="inlineStr">
         <is>
           <t>הרב אהרן קוטלר</t>
         </is>
       </c>
-      <c r="D563" t="inlineStr">
+      <c r="D563" s="3" t="inlineStr">
         <is>
           <t>1891–1962</t>
         </is>
       </c>
-      <c r="E563" t="inlineStr">
+      <c r="E563" s="3" t="inlineStr">
         <is>
           <t>ארה"ב</t>
         </is>
       </c>
-      <c r="F563" t="inlineStr">
+      <c r="F563" s="3" t="inlineStr">
         <is>
           <t>מודרני</t>
         </is>
       </c>
-      <c r="G563" t="inlineStr">
+      <c r="G563" s="3" t="inlineStr">
         <is>
           <t>ראשות ישיבה</t>
         </is>
       </c>
-      <c r="H563" t="inlineStr"/>
-      <c r="I563" t="inlineStr">
+      <c r="H563" s="3" t="inlineStr"/>
+      <c r="I563" s="3" t="inlineStr">
         <is>
           <t>מייסד ישיבת לייקווד ואדריכל עולם התורה באמריקה שלאחר השואה. העמיד את לימוד התורה לשמה כערך עליון ללא פשרות.</t>
         </is>
       </c>
-      <c r="J563" t="inlineStr"/>
+      <c r="J563" s="3" t="inlineStr"/>
     </row>
     <row r="564">
-      <c r="A564" t="inlineStr">
+      <c r="A564" s="3" t="inlineStr">
         <is>
           <t>563</t>
         </is>
       </c>
-      <c r="B564" t="inlineStr">
+      <c r="B564" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C564" t="inlineStr">
+      <c r="C564" s="3" t="inlineStr">
         <is>
           <t>הרב יוסף יצחק שניאורסון (הריי"צ)</t>
         </is>
       </c>
-      <c r="D564" t="inlineStr">
+      <c r="D564" s="3" t="inlineStr">
         <is>
           <t>1880–1950</t>
         </is>
       </c>
-      <c r="E564" t="inlineStr">
+      <c r="E564" s="3" t="inlineStr">
         <is>
           <t>ארה"ב</t>
         </is>
       </c>
-      <c r="F564" t="inlineStr">
+      <c r="F564" s="3" t="inlineStr">
         <is>
           <t>מודרני</t>
         </is>
       </c>
-      <c r="G564" t="inlineStr">
+      <c r="G564" s="3" t="inlineStr">
         <is>
           <t>חסידות, הנהגה</t>
         </is>
       </c>
-      <c r="H564" t="inlineStr"/>
-      <c r="I564" t="inlineStr">
+      <c r="H564" s="3" t="inlineStr"/>
+      <c r="I564" s="3" t="inlineStr">
         <is>
           <t>האדמו"ר השישי של חב"ד. עמד בעוז מול השלטון הסובייטי, שוחרר ממאסר מוות, והעביר את מרכז חב"ד לאמריקה.</t>
         </is>
       </c>
-      <c r="J564" t="inlineStr"/>
+      <c r="J564" s="3" t="inlineStr"/>
     </row>
     <row r="565">
-      <c r="A565" t="inlineStr">
+      <c r="A565" s="3" t="inlineStr">
         <is>
           <t>564</t>
         </is>
       </c>
-      <c r="B565" t="inlineStr">
+      <c r="B565" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C565" t="inlineStr">
+      <c r="C565" s="3" t="inlineStr">
         <is>
           <t>הרב לורד יונתן זקס</t>
         </is>
       </c>
-      <c r="D565" t="inlineStr">
+      <c r="D565" s="3" t="inlineStr">
         <is>
           <t>1948–2020</t>
         </is>
       </c>
-      <c r="E565" t="inlineStr">
+      <c r="E565" s="3" t="inlineStr">
         <is>
           <t>אנגליה</t>
         </is>
       </c>
-      <c r="F565" t="inlineStr">
+      <c r="F565" s="3" t="inlineStr">
         <is>
           <t>מודרני</t>
         </is>
       </c>
-      <c r="G565" t="inlineStr">
+      <c r="G565" s="3" t="inlineStr">
         <is>
           <t>הגות, הנהגה</t>
         </is>
       </c>
-      <c r="H565" t="inlineStr"/>
-      <c r="I565" t="inlineStr">
+      <c r="H565" s="3" t="inlineStr"/>
+      <c r="I565" s="3" t="inlineStr">
         <is>
           <t>רבה הראשי של בריטניה והוגה יהודי בעל השפעה עולמית. הציג את קול התורה בשפת הפילוסופיה והמוסר האוניברסלי.</t>
         </is>
       </c>
-      <c r="J565" t="inlineStr"/>
+      <c r="J565" s="3" t="inlineStr"/>
     </row>
     <row r="566">
-      <c r="A566" t="inlineStr">
+      <c r="A566" s="3" t="inlineStr">
         <is>
           <t>565</t>
         </is>
       </c>
-      <c r="B566" t="inlineStr">
+      <c r="B566" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C566" t="inlineStr">
+      <c r="C566" s="3" t="inlineStr">
         <is>
           <t>הרב מרדכי עטיה</t>
         </is>
       </c>
-      <c r="D566" t="inlineStr">
+      <c r="D566" s="3" t="inlineStr">
         <is>
           <t>1883–1978</t>
         </is>
       </c>
-      <c r="E566" t="inlineStr">
+      <c r="E566" s="3" t="inlineStr">
         <is>
           <t>ירושלים</t>
         </is>
       </c>
-      <c r="F566" t="inlineStr">
+      <c r="F566" s="3" t="inlineStr">
         <is>
           <t>מודרני</t>
         </is>
       </c>
-      <c r="G566" t="inlineStr">
+      <c r="G566" s="3" t="inlineStr">
         <is>
           <t>קבלה</t>
         </is>
       </c>
-      <c r="H566" t="inlineStr"/>
-      <c r="I566" t="inlineStr">
+      <c r="H566" s="3" t="inlineStr"/>
+      <c r="I566" s="3" t="inlineStr">
         <is>
           <t>מקובל וראש ישיבת המקובלים, מחכמי ארם צובא שקבעו משכנם בירושלים. קרא לגאולה מתוך תורת הסוד ומעשה.</t>
         </is>
       </c>
-      <c r="J566" t="inlineStr"/>
+      <c r="J566" s="3" t="inlineStr"/>
     </row>
     <row r="567">
-      <c r="A567" t="inlineStr">
+      <c r="A567" s="3" t="inlineStr">
         <is>
           <t>566</t>
         </is>
       </c>
-      <c r="B567" t="inlineStr">
+      <c r="B567" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C567" t="inlineStr">
+      <c r="C567" s="3" t="inlineStr">
         <is>
           <t>הרב משה צוריאל</t>
         </is>
       </c>
-      <c r="D567" t="inlineStr">
+      <c r="D567" s="3" t="inlineStr">
         <is>
           <t>1938–2023</t>
         </is>
       </c>
-      <c r="E567" t="inlineStr">
+      <c r="E567" s="3" t="inlineStr">
         <is>
           <t>בני ברק</t>
         </is>
       </c>
-      <c r="F567" t="inlineStr">
+      <c r="F567" s="3" t="inlineStr">
         <is>
           <t>מודרני</t>
         </is>
       </c>
-      <c r="G567" t="inlineStr">
+      <c r="G567" s="3" t="inlineStr">
         <is>
           <t>מוסר, מחשבה, קבלה</t>
         </is>
       </c>
-      <c r="H567" t="inlineStr"/>
-      <c r="I567" t="inlineStr">
+      <c r="H567" s="3" t="inlineStr"/>
+      <c r="I567" s="3" t="inlineStr">
         <is>
           <t>משגיח ישיבת 'שעלבים' ומחבר פורה. כינס וביאר את כתבי הראי"ה קוק, הגר"א והרמח"ל — גשר בין עולם המוסר לתורת ארץ ישראל.</t>
         </is>
       </c>
-      <c r="J567" t="inlineStr"/>
+      <c r="J567" s="3" t="inlineStr"/>
     </row>
     <row r="568">
-      <c r="A568" t="inlineStr">
+      <c r="A568" s="3" t="inlineStr">
         <is>
           <t>567</t>
         </is>
       </c>
-      <c r="B568" t="inlineStr">
+      <c r="B568" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C568" t="inlineStr">
+      <c r="C568" s="3" t="inlineStr">
         <is>
           <t>הרב שלמה קרליבך</t>
         </is>
       </c>
-      <c r="D568" t="inlineStr">
+      <c r="D568" s="3" t="inlineStr">
         <is>
           <t>1925–1994</t>
         </is>
       </c>
-      <c r="E568" t="inlineStr">
+      <c r="E568" s="3" t="inlineStr">
         <is>
           <t>ארה"ב</t>
         </is>
       </c>
-      <c r="F568" t="inlineStr">
+      <c r="F568" s="3" t="inlineStr">
         <is>
           <t>מודרני</t>
         </is>
       </c>
-      <c r="G568" t="inlineStr">
+      <c r="G568" s="3" t="inlineStr">
         <is>
           <t>נגינה, קירוב</t>
         </is>
       </c>
-      <c r="H568" t="inlineStr"/>
-      <c r="I568" t="inlineStr">
+      <c r="H568" s="3" t="inlineStr"/>
+      <c r="I568" s="3" t="inlineStr">
         <is>
           <t>'הרבי המרקד' — מחולל מהפכת הנגינה היהודית בדור התשובה. ניגוניו ופתיחת לבו קירבו רבבות ליהדות.</t>
         </is>
       </c>
-      <c r="J568" t="inlineStr"/>
+      <c r="J568" s="3" t="inlineStr"/>
     </row>
     <row r="569">
-      <c r="A569" t="inlineStr">
+      <c r="A569" s="3" t="inlineStr">
         <is>
           <t>568</t>
         </is>
       </c>
-      <c r="B569" t="inlineStr">
+      <c r="B569" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C569" t="inlineStr">
+      <c r="C569" s="3" t="inlineStr">
         <is>
           <t>יהודית</t>
         </is>
       </c>
-      <c r="D569" t="inlineStr">
+      <c r="D569" s="3" t="inlineStr">
         <is>
           <t>170–100 לפנה״ס</t>
         </is>
       </c>
-      <c r="E569" t="inlineStr">
+      <c r="E569" s="3" t="inlineStr">
         <is>
           <t>ארץ ישראל</t>
         </is>
       </c>
-      <c r="F569" t="inlineStr">
+      <c r="F569" s="3" t="inlineStr">
         <is>
           <t>בית שני</t>
         </is>
       </c>
-      <c r="G569" t="inlineStr">
+      <c r="G569" s="3" t="inlineStr">
         <is>
           <t>גבורה</t>
         </is>
       </c>
-      <c r="H569" t="inlineStr">
+      <c r="H569" s="3" t="inlineStr">
         <is>
           <t>נשים</t>
         </is>
       </c>
-      <c r="I569" t="inlineStr">
+      <c r="I569" s="3" t="inlineStr">
         <is>
           <t>גיבורת הספר החיצוני הקרוי על שמה, שמסרה נפשה להצלת עמה. דמותה נקשרה במסורת לנס חנוכה.</t>
         </is>
       </c>
-      <c r="J569" t="inlineStr"/>
+      <c r="J569" s="3" t="inlineStr"/>
     </row>
     <row r="570">
-      <c r="A570" t="inlineStr">
+      <c r="A570" s="3" t="inlineStr">
         <is>
           <t>569</t>
         </is>
       </c>
-      <c r="B570" t="inlineStr">
+      <c r="B570" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C570" t="inlineStr">
+      <c r="C570" s="3" t="inlineStr">
         <is>
           <t>יוסל מרוסהיים</t>
         </is>
       </c>
-      <c r="D570" t="inlineStr">
+      <c r="D570" s="3" t="inlineStr">
         <is>
           <t>1476–1554</t>
         </is>
       </c>
-      <c r="E570" t="inlineStr">
+      <c r="E570" s="3" t="inlineStr">
         <is>
           <t>אשכנז</t>
         </is>
       </c>
-      <c r="F570" t="inlineStr">
+      <c r="F570" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G570" t="inlineStr">
+      <c r="G570" s="3" t="inlineStr">
         <is>
           <t>שתדלנות, הנהגה</t>
         </is>
       </c>
-      <c r="H570" t="inlineStr"/>
-      <c r="I570" t="inlineStr">
+      <c r="H570" s="3" t="inlineStr"/>
+      <c r="I570" s="3" t="inlineStr">
         <is>
           <t>השתדלן הגדול של יהדות אשכנז מול הקיסר קרל החמישי. 'ספר המקנה' שלו — עדות אישית להנהגה בדור של גזרות ורפורמציה.</t>
         </is>
       </c>
-      <c r="J570" t="inlineStr"/>
+      <c r="J570" s="3" t="inlineStr"/>
     </row>
     <row r="571">
-      <c r="A571" t="inlineStr">
+      <c r="A571" s="3" t="inlineStr">
         <is>
           <t>570</t>
         </is>
       </c>
-      <c r="B571" t="inlineStr">
+      <c r="B571" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C571" t="inlineStr">
+      <c r="C571" s="3" t="inlineStr">
         <is>
           <t>יעקב אבינו</t>
         </is>
       </c>
-      <c r="D571" t="inlineStr">
+      <c r="D571" s="3" t="inlineStr">
         <is>
           <t>1652–1505 לפנה״ס</t>
         </is>
       </c>
-      <c r="E571" t="inlineStr">
+      <c r="E571" s="3" t="inlineStr">
         <is>
           <t>חברון</t>
         </is>
       </c>
-      <c r="F571" t="inlineStr">
+      <c r="F571" s="3" t="inlineStr">
         <is>
           <t>האבות</t>
         </is>
       </c>
-      <c r="G571" t="inlineStr">
+      <c r="G571" s="3" t="inlineStr">
         <is>
           <t>תורה, אמת</t>
         </is>
       </c>
-      <c r="H571" t="inlineStr"/>
-      <c r="I571" t="inlineStr">
+      <c r="H571" s="3" t="inlineStr"/>
+      <c r="I571" s="3" t="inlineStr">
         <is>
           <t>בחיר האבות ואבי שנים־עשר השבטים. 'איש תם יושב אוהלים' שירד למצרים והניח את יסוד בית ישראל.</t>
         </is>
       </c>
-      <c r="J571" t="inlineStr"/>
+      <c r="J571" s="3" t="inlineStr"/>
     </row>
     <row r="572">
-      <c r="A572" t="inlineStr">
+      <c r="A572" s="3" t="inlineStr">
         <is>
           <t>571</t>
         </is>
       </c>
-      <c r="B572" t="inlineStr">
+      <c r="B572" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C572" t="inlineStr">
+      <c r="C572" s="3" t="inlineStr">
         <is>
           <t>יצחק אבינו</t>
         </is>
       </c>
-      <c r="D572" t="inlineStr">
+      <c r="D572" s="3" t="inlineStr">
         <is>
           <t>1712–1532 לפנה״ס</t>
         </is>
       </c>
-      <c r="E572" t="inlineStr">
+      <c r="E572" s="3" t="inlineStr">
         <is>
           <t>חברון</t>
         </is>
       </c>
-      <c r="F572" t="inlineStr">
+      <c r="F572" s="3" t="inlineStr">
         <is>
           <t>האבות</t>
         </is>
       </c>
-      <c r="G572" t="inlineStr">
+      <c r="G572" s="3" t="inlineStr">
         <is>
           <t>גבורה, תפילה</t>
         </is>
       </c>
-      <c r="H572" t="inlineStr"/>
-      <c r="I572" t="inlineStr">
+      <c r="H572" s="3" t="inlineStr"/>
+      <c r="I572" s="3" t="inlineStr">
         <is>
           <t>השני שבאבות. נעקד על גבי המזבח בהר המוריה, וחפר מחדש את בארות אביו — ממשיך הדרך בארץ.</t>
         </is>
       </c>
-      <c r="J572" t="inlineStr"/>
+      <c r="J572" s="3" t="inlineStr"/>
     </row>
     <row r="573">
-      <c r="A573" t="inlineStr">
+      <c r="A573" s="3" t="inlineStr">
         <is>
           <t>572</t>
         </is>
       </c>
-      <c r="B573" t="inlineStr">
+      <c r="B573" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C573" t="inlineStr">
+      <c r="C573" s="3" t="inlineStr">
         <is>
           <t>ישעיהו הנביא</t>
         </is>
       </c>
-      <c r="D573" t="inlineStr">
+      <c r="D573" s="3" t="inlineStr">
         <is>
           <t>765–695 לפנה״ס</t>
         </is>
       </c>
-      <c r="E573" t="inlineStr">
+      <c r="E573" s="3" t="inlineStr">
         <is>
           <t>ירושלים</t>
         </is>
       </c>
-      <c r="F573" t="inlineStr">
+      <c r="F573" s="3" t="inlineStr">
         <is>
           <t>המלכים</t>
         </is>
       </c>
-      <c r="G573" t="inlineStr">
+      <c r="G573" s="3" t="inlineStr">
         <is>
           <t>נבואה</t>
         </is>
       </c>
-      <c r="H573" t="inlineStr"/>
-      <c r="I573" t="inlineStr">
+      <c r="H573" s="3" t="inlineStr"/>
+      <c r="I573" s="3" t="inlineStr">
         <is>
           <t>מגדולי נביאי הכתב. נבואות החורבן והנחמה שלו — 'נחמו נחמו עמי' — מלוות את ישראל בכל הדורות.</t>
         </is>
       </c>
-      <c r="J573" t="inlineStr"/>
+      <c r="J573" s="3" t="inlineStr"/>
     </row>
     <row r="574">
-      <c r="A574" t="inlineStr">
+      <c r="A574" s="3" t="inlineStr">
         <is>
           <t>573</t>
         </is>
       </c>
-      <c r="B574" t="inlineStr">
+      <c r="B574" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C574" t="inlineStr">
+      <c r="C574" s="3" t="inlineStr">
         <is>
           <t>מהר"י בירב (רבי יעקב בירב)</t>
         </is>
       </c>
-      <c r="D574" t="inlineStr">
+      <c r="D574" s="3" t="inlineStr">
         <is>
           <t>1474–1546</t>
         </is>
       </c>
-      <c r="E574" t="inlineStr">
+      <c r="E574" s="3" t="inlineStr">
         <is>
           <t>צפת</t>
         </is>
       </c>
-      <c r="F574" t="inlineStr">
+      <c r="F574" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G574" t="inlineStr">
+      <c r="G574" s="3" t="inlineStr">
         <is>
           <t>הלכה</t>
         </is>
       </c>
-      <c r="H574" t="inlineStr"/>
-      <c r="I574" t="inlineStr">
+      <c r="H574" s="3" t="inlineStr"/>
+      <c r="I574" s="3" t="inlineStr">
         <is>
           <t>גדול חכמי צפת בדורו ויוזם חידוש הסמיכה (1538) כצעד לקירוב הגאולה — מהלך שהצית את הפולמוס הגדול עם חכמי ירושלים.</t>
         </is>
       </c>
-      <c r="J574" t="inlineStr"/>
+      <c r="J574" s="3" t="inlineStr"/>
     </row>
     <row r="575">
-      <c r="A575" t="inlineStr">
+      <c r="A575" s="3" t="inlineStr">
         <is>
           <t>574</t>
         </is>
       </c>
-      <c r="B575" t="inlineStr">
+      <c r="B575" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C575" t="inlineStr">
+      <c r="C575" s="3" t="inlineStr">
         <is>
           <t>משה רבנו</t>
         </is>
       </c>
-      <c r="D575" t="inlineStr">
+      <c r="D575" s="3" t="inlineStr">
         <is>
           <t>1391–1271 לפנה״ס</t>
         </is>
       </c>
-      <c r="E575" t="inlineStr">
+      <c r="E575" s="3" t="inlineStr">
         <is>
           <t>מצרים</t>
         </is>
       </c>
-      <c r="F575" t="inlineStr">
+      <c r="F575" s="3" t="inlineStr">
         <is>
           <t>יציאת מצרים</t>
         </is>
       </c>
-      <c r="G575" t="inlineStr">
+      <c r="G575" s="3" t="inlineStr">
         <is>
           <t>תורה, נבואה, הנהגה</t>
         </is>
       </c>
-      <c r="H575" t="inlineStr"/>
-      <c r="I575" t="inlineStr">
+      <c r="H575" s="3" t="inlineStr"/>
+      <c r="I575" s="3" t="inlineStr">
         <is>
           <t>אדון הנביאים ומקבל התורה בסיני. הוציא את ישראל ממצרים, קיבל את הלוחות ומסר תורה לכל ישראל — ראש שלשלת הקבלה.</t>
         </is>
       </c>
-      <c r="J575" t="inlineStr">
+      <c r="J575" s="3" t="inlineStr">
         <is>
           <t>משה קיבל תורה מסיני ומסרה ליהושע (אבות א, א)</t>
         </is>
       </c>
     </row>
     <row r="576">
-      <c r="A576" t="inlineStr">
+      <c r="A576" s="3" t="inlineStr">
         <is>
           <t>575</t>
         </is>
       </c>
-      <c r="B576" t="inlineStr">
+      <c r="B576" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C576" t="inlineStr">
+      <c r="C576" s="3" t="inlineStr">
         <is>
           <t>עזרא הסופר</t>
         </is>
       </c>
-      <c r="D576" t="inlineStr">
+      <c r="D576" s="3" t="inlineStr">
         <is>
           <t>480–420 לפנה״ס</t>
         </is>
       </c>
-      <c r="E576" t="inlineStr">
+      <c r="E576" s="3" t="inlineStr">
         <is>
           <t>ירושלים</t>
         </is>
       </c>
-      <c r="F576" t="inlineStr">
+      <c r="F576" s="3" t="inlineStr">
         <is>
           <t>בית שני</t>
         </is>
       </c>
-      <c r="G576" t="inlineStr">
+      <c r="G576" s="3" t="inlineStr">
         <is>
           <t>תורה, הנהגה</t>
         </is>
       </c>
-      <c r="H576" t="inlineStr"/>
-      <c r="I576" t="inlineStr">
+      <c r="H576" s="3" t="inlineStr"/>
+      <c r="I576" s="3" t="inlineStr">
         <is>
           <t>מחדש התורה בישראל בראשית ימי הבית השני. העלה את הגולה מבבל, כונן את קריאת התורה ברבים — 'ראוי היה עזרא שתינתן תורה על ידו'.</t>
         </is>
       </c>
-      <c r="J576" t="inlineStr"/>
+      <c r="J576" s="3" t="inlineStr"/>
     </row>
     <row r="577">
-      <c r="A577" t="inlineStr">
+      <c r="A577" s="3" t="inlineStr">
         <is>
           <t>576</t>
         </is>
       </c>
-      <c r="B577" t="inlineStr">
+      <c r="B577" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C577" t="inlineStr">
+      <c r="C577" s="3" t="inlineStr">
         <is>
           <t>רב הונא</t>
         </is>
       </c>
-      <c r="D577" t="inlineStr">
+      <c r="D577" s="3" t="inlineStr">
         <is>
           <t>216–296</t>
         </is>
       </c>
-      <c r="E577" t="inlineStr">
+      <c r="E577" s="3" t="inlineStr">
         <is>
           <t>סורא</t>
         </is>
       </c>
-      <c r="F577" t="inlineStr">
+      <c r="F577" s="3" t="inlineStr">
         <is>
           <t>אמוראים</t>
         </is>
       </c>
-      <c r="G577" t="inlineStr">
+      <c r="G577" s="3" t="inlineStr">
         <is>
           <t>הלכה</t>
         </is>
       </c>
-      <c r="H577" t="inlineStr"/>
-      <c r="I577" t="inlineStr">
+      <c r="H577" s="3" t="inlineStr"/>
+      <c r="I577" s="3" t="inlineStr">
         <is>
           <t>עמוד התווך של הדור השני לאמוראי בבל וראש ישיבת סורא ארבעים שנה. הלכה כמותו בממונות ברוב מחלוקותיו.</t>
         </is>
       </c>
-      <c r="J577" t="inlineStr"/>
+      <c r="J577" s="3" t="inlineStr"/>
     </row>
     <row r="578">
-      <c r="A578" t="inlineStr">
+      <c r="A578" s="3" t="inlineStr">
         <is>
           <t>577</t>
         </is>
       </c>
-      <c r="B578" t="inlineStr">
+      <c r="B578" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C578" t="inlineStr">
+      <c r="C578" s="3" t="inlineStr">
         <is>
           <t>רבי אבון הגדול</t>
         </is>
       </c>
-      <c r="D578" t="inlineStr">
+      <c r="D578" s="3" t="inlineStr">
         <is>
           <t>900–960</t>
         </is>
       </c>
-      <c r="E578" t="inlineStr">
+      <c r="E578" s="3" t="inlineStr">
         <is>
           <t>מגנצא</t>
         </is>
       </c>
-      <c r="F578" t="inlineStr">
+      <c r="F578" s="3" t="inlineStr">
         <is>
           <t>גאונים</t>
         </is>
       </c>
-      <c r="G578" t="inlineStr">
+      <c r="G578" s="3" t="inlineStr">
         <is>
           <t>תורה, פיוט</t>
         </is>
       </c>
-      <c r="H578" t="inlineStr"/>
-      <c r="I578" t="inlineStr">
+      <c r="H578" s="3" t="inlineStr"/>
+      <c r="I578" s="3" t="inlineStr">
         <is>
           <t>מאבות הקהילה הרבנית הקדומה ברינוס. ממניחי היסוד לתרבות התורה של אשכנז הקדומה, דורות לפני רבנו גרשום.</t>
         </is>
       </c>
-      <c r="J578" t="inlineStr"/>
+      <c r="J578" s="3" t="inlineStr"/>
     </row>
     <row r="579">
-      <c r="A579" t="inlineStr">
+      <c r="A579" s="3" t="inlineStr">
         <is>
           <t>578</t>
         </is>
       </c>
-      <c r="B579" t="inlineStr">
+      <c r="B579" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C579" t="inlineStr">
+      <c r="C579" s="3" t="inlineStr">
         <is>
           <t>רבי טרפון</t>
         </is>
       </c>
-      <c r="D579" t="inlineStr">
+      <c r="D579" s="3" t="inlineStr">
         <is>
           <t>46–117</t>
         </is>
       </c>
-      <c r="E579" t="inlineStr">
+      <c r="E579" s="3" t="inlineStr">
         <is>
           <t>יבנה</t>
         </is>
       </c>
-      <c r="F579" t="inlineStr">
+      <c r="F579" s="3" t="inlineStr">
         <is>
           <t>תנאים</t>
         </is>
       </c>
-      <c r="G579" t="inlineStr">
+      <c r="G579" s="3" t="inlineStr">
         <is>
           <t>הלכה</t>
         </is>
       </c>
-      <c r="H579" t="inlineStr"/>
-      <c r="I579" t="inlineStr">
+      <c r="H579" s="3" t="inlineStr"/>
+      <c r="I579" s="3" t="inlineStr">
         <is>
           <t>מגדולי תנאי יבנה, כהן שזכה לשרת במקדש. בר פלוגתא ואוהבו של רבי עקיבא; 'היום קצר והמלאכה מרובה'.</t>
         </is>
       </c>
-      <c r="J579" t="inlineStr"/>
+      <c r="J579" s="3" t="inlineStr"/>
     </row>
     <row r="580">
-      <c r="A580" t="inlineStr">
+      <c r="A580" s="3" t="inlineStr">
         <is>
           <t>579</t>
         </is>
       </c>
-      <c r="B580" t="inlineStr">
+      <c r="B580" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C580" t="inlineStr">
+      <c r="C580" s="3" t="inlineStr">
         <is>
           <t>רבי יהודה הלוי (ריה"ל)</t>
         </is>
       </c>
-      <c r="D580" t="inlineStr">
+      <c r="D580" s="3" t="inlineStr">
         <is>
           <t>1075–1141</t>
         </is>
       </c>
-      <c r="E580" t="inlineStr">
+      <c r="E580" s="3" t="inlineStr">
         <is>
           <t>טולדו</t>
         </is>
       </c>
-      <c r="F580" t="inlineStr">
+      <c r="F580" s="3" t="inlineStr">
         <is>
           <t>ראשונים</t>
         </is>
       </c>
-      <c r="G580" t="inlineStr">
+      <c r="G580" s="3" t="inlineStr">
         <is>
           <t>שירה, הגות</t>
         </is>
       </c>
-      <c r="H580" t="inlineStr"/>
-      <c r="I580" t="inlineStr">
+      <c r="H580" s="3" t="inlineStr"/>
+      <c r="I580" s="3" t="inlineStr">
         <is>
           <t>מגדולי משוררי ספרד והוגה 'הכוזרי'. שירת געגועיו לציון — 'לבי במזרח ואנוכי בסוף מערב' — מלווה את האומה; בסוף ימיו יצא לארץ ישראל.</t>
         </is>
       </c>
-      <c r="J580" t="inlineStr"/>
+      <c r="J580" s="3" t="inlineStr"/>
     </row>
     <row r="581">
-      <c r="A581" t="inlineStr">
+      <c r="A581" s="3" t="inlineStr">
         <is>
           <t>580</t>
         </is>
       </c>
-      <c r="B581" t="inlineStr">
+      <c r="B581" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C581" t="inlineStr">
+      <c r="C581" s="3" t="inlineStr">
         <is>
           <t>רבי יהודה הנשיא</t>
         </is>
       </c>
-      <c r="D581" t="inlineStr">
+      <c r="D581" s="3" t="inlineStr">
         <is>
           <t>135–217</t>
         </is>
       </c>
-      <c r="E581" t="inlineStr">
+      <c r="E581" s="3" t="inlineStr">
         <is>
           <t>ציפורי</t>
         </is>
       </c>
-      <c r="F581" t="inlineStr">
+      <c r="F581" s="3" t="inlineStr">
         <is>
           <t>תנאים</t>
         </is>
       </c>
-      <c r="G581" t="inlineStr">
+      <c r="G581" s="3" t="inlineStr">
         <is>
           <t>משנה, הנהגה</t>
         </is>
       </c>
-      <c r="H581" t="inlineStr"/>
-      <c r="I581" t="inlineStr">
+      <c r="H581" s="3" t="inlineStr"/>
+      <c r="I581" s="3" t="inlineStr">
         <is>
           <t>עורך המשנה וחותם תקופת התנאים. איחד את מסורות התורה שבעל פה לחיבור אחד מוסמך, ושילב גדולה בתורה עם עושר ומנהיגות מול רומא.</t>
         </is>
       </c>
-      <c r="J581" t="inlineStr">
+      <c r="J581" s="3" t="inlineStr">
         <is>
           <t>עריכת המשנה — חתימת התורה שבעל פה הראשונה</t>
         </is>
       </c>
     </row>
     <row r="582">
-      <c r="A582" t="inlineStr">
+      <c r="A582" s="3" t="inlineStr">
         <is>
           <t>581</t>
         </is>
       </c>
-      <c r="B582" t="inlineStr">
+      <c r="B582" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C582" t="inlineStr">
+      <c r="C582" s="3" t="inlineStr">
         <is>
           <t>רבי יעקב הכהן (המקובל)</t>
         </is>
       </c>
-      <c r="D582" t="inlineStr">
+      <c r="D582" s="3" t="inlineStr">
         <is>
           <t>1200–1270</t>
         </is>
       </c>
-      <c r="E582" t="inlineStr">
+      <c r="E582" s="3" t="inlineStr">
         <is>
           <t>קאסטיליה</t>
         </is>
       </c>
-      <c r="F582" t="inlineStr">
+      <c r="F582" s="3" t="inlineStr">
         <is>
           <t>ראשונים</t>
         </is>
       </c>
-      <c r="G582" t="inlineStr">
+      <c r="G582" s="3" t="inlineStr">
         <is>
           <t>קבלה</t>
         </is>
       </c>
-      <c r="H582" t="inlineStr"/>
-      <c r="I582" t="inlineStr">
+      <c r="H582" s="3" t="inlineStr"/>
+      <c r="I582" s="3" t="inlineStr">
         <is>
           <t>ממקובלי קאסטיליה הראשונים, מאבות 'קבלת האחים הכהנים'. חיבוריו על האותיות והמרכבה קדמו לזוהר והשפיעו עליו.</t>
         </is>
       </c>
-      <c r="J582" t="inlineStr"/>
+      <c r="J582" s="3" t="inlineStr"/>
     </row>
     <row r="583">
-      <c r="A583" t="inlineStr">
+      <c r="A583" s="3" t="inlineStr">
         <is>
           <t>582</t>
         </is>
       </c>
-      <c r="B583" t="inlineStr">
+      <c r="B583" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C583" t="inlineStr">
+      <c r="C583" s="3" t="inlineStr">
         <is>
           <t>רבי יצחק אלפסי (הרי"ף)</t>
         </is>
       </c>
-      <c r="D583" t="inlineStr">
+      <c r="D583" s="3" t="inlineStr">
         <is>
           <t>1013–1103</t>
         </is>
       </c>
-      <c r="E583" t="inlineStr">
+      <c r="E583" s="3" t="inlineStr">
         <is>
           <t>פאס</t>
         </is>
       </c>
-      <c r="F583" t="inlineStr">
+      <c r="F583" s="3" t="inlineStr">
         <is>
           <t>ראשונים</t>
         </is>
       </c>
-      <c r="G583" t="inlineStr">
+      <c r="G583" s="3" t="inlineStr">
         <is>
           <t>הלכה</t>
         </is>
       </c>
-      <c r="H583" t="inlineStr"/>
-      <c r="I583" t="inlineStr">
+      <c r="H583" s="3" t="inlineStr"/>
+      <c r="I583" s="3" t="inlineStr">
         <is>
           <t>גדול פוסקי הדור שבין הגאונים לראשונים. 'הלכות הרי"ף' זיקקו את התלמוד לפסק הלכה ושימשו עמוד יסוד לשולחן ערוך.</t>
         </is>
       </c>
-      <c r="J583" t="inlineStr"/>
+      <c r="J583" s="3" t="inlineStr"/>
     </row>
     <row r="584">
-      <c r="A584" t="inlineStr">
+      <c r="A584" s="3" t="inlineStr">
         <is>
           <t>583</t>
         </is>
       </c>
-      <c r="B584" t="inlineStr">
+      <c r="B584" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C584" t="inlineStr">
+      <c r="C584" s="3" t="inlineStr">
         <is>
           <t>רבי יצחק הלוי (סגן לויה)</t>
         </is>
       </c>
-      <c r="D584" t="inlineStr">
+      <c r="D584" s="3" t="inlineStr">
         <is>
           <t>1000–1080</t>
         </is>
       </c>
-      <c r="E584" t="inlineStr">
+      <c r="E584" s="3" t="inlineStr">
         <is>
           <t>וורמייזא</t>
         </is>
       </c>
-      <c r="F584" t="inlineStr">
+      <c r="F584" s="3" t="inlineStr">
         <is>
           <t>ראשונים</t>
         </is>
       </c>
-      <c r="G584" t="inlineStr">
+      <c r="G584" s="3" t="inlineStr">
         <is>
           <t>תלמוד, פרשנות</t>
         </is>
       </c>
-      <c r="H584" t="inlineStr"/>
-      <c r="I584" t="inlineStr">
+      <c r="H584" s="3" t="inlineStr"/>
+      <c r="I584" s="3" t="inlineStr">
         <is>
           <t>מראשי ישיבות לותיר ורבותיו המובהקים של רש"י בוורמייזא. ממעצבי מסורת הלימוד האשכנזית הקדומה.</t>
         </is>
       </c>
-      <c r="J584" t="inlineStr"/>
+      <c r="J584" s="3" t="inlineStr"/>
     </row>
     <row r="585">
-      <c r="A585" t="inlineStr">
+      <c r="A585" s="3" t="inlineStr">
         <is>
           <t>584</t>
         </is>
       </c>
-      <c r="B585" t="inlineStr">
+      <c r="B585" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C585" t="inlineStr">
+      <c r="C585" s="3" t="inlineStr">
         <is>
           <t>רבי ישמעאל (בן אלישע)</t>
         </is>
       </c>
-      <c r="D585" t="inlineStr">
+      <c r="D585" s="3" t="inlineStr">
         <is>
           <t>60–135</t>
         </is>
       </c>
-      <c r="E585" t="inlineStr">
+      <c r="E585" s="3" t="inlineStr">
         <is>
           <t>ארץ ישראל</t>
         </is>
       </c>
-      <c r="F585" t="inlineStr">
+      <c r="F585" s="3" t="inlineStr">
         <is>
           <t>תנאים</t>
         </is>
       </c>
-      <c r="G585" t="inlineStr">
+      <c r="G585" s="3" t="inlineStr">
         <is>
           <t>מדרש הלכה</t>
         </is>
       </c>
-      <c r="H585" t="inlineStr"/>
-      <c r="I585" t="inlineStr">
+      <c r="H585" s="3" t="inlineStr"/>
+      <c r="I585" s="3" t="inlineStr">
         <is>
           <t>אב עולם ובעל שלוש-עשרה המידות שהתורה נדרשת בהן. בר פלוגתא הגדול של רבי עקיבא בדרכי המדרש — 'דיברה תורה כלשון בני אדם'.</t>
         </is>
       </c>
-      <c r="J585" t="inlineStr"/>
+      <c r="J585" s="3" t="inlineStr"/>
     </row>
     <row r="586">
-      <c r="A586" t="inlineStr">
+      <c r="A586" s="3" t="inlineStr">
         <is>
           <t>585</t>
         </is>
       </c>
-      <c r="B586" t="inlineStr">
+      <c r="B586" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C586" t="inlineStr">
+      <c r="C586" s="3" t="inlineStr">
         <is>
           <t>רבי לוי בן חביב (המהרלב"ח)</t>
         </is>
       </c>
-      <c r="D586" t="inlineStr">
+      <c r="D586" s="3" t="inlineStr">
         <is>
           <t>1483–1545</t>
         </is>
       </c>
-      <c r="E586" t="inlineStr">
+      <c r="E586" s="3" t="inlineStr">
         <is>
           <t>ירושלים</t>
         </is>
       </c>
-      <c r="F586" t="inlineStr">
+      <c r="F586" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G586" t="inlineStr">
+      <c r="G586" s="3" t="inlineStr">
         <is>
           <t>הלכה</t>
         </is>
       </c>
-      <c r="H586" t="inlineStr"/>
-      <c r="I586" t="inlineStr">
+      <c r="H586" s="3" t="inlineStr"/>
+      <c r="I586" s="3" t="inlineStr">
         <is>
           <t>רבה של ירושלים והמתנגד הגדול לחידוש הסמיכה. 'קונטרס הסמיכה' שלו הכריע את הפולמוס ההלכתי הנודע מול חכמי צפת.</t>
         </is>
       </c>
-      <c r="J586" t="inlineStr"/>
+      <c r="J586" s="3" t="inlineStr"/>
     </row>
     <row r="587">
-      <c r="A587" t="inlineStr">
+      <c r="A587" s="3" t="inlineStr">
         <is>
           <t>586</t>
         </is>
       </c>
-      <c r="B587" t="inlineStr">
+      <c r="B587" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C587" t="inlineStr">
+      <c r="C587" s="3" t="inlineStr">
         <is>
           <t>רבי משה אלשקר (מהר"ם אלשקר)</t>
         </is>
       </c>
-      <c r="D587" t="inlineStr">
+      <c r="D587" s="3" t="inlineStr">
         <is>
           <t>1466–1542</t>
         </is>
       </c>
-      <c r="E587" t="inlineStr">
+      <c r="E587" s="3" t="inlineStr">
         <is>
           <t>מצרים</t>
         </is>
       </c>
-      <c r="F587" t="inlineStr">
+      <c r="F587" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G587" t="inlineStr">
+      <c r="G587" s="3" t="inlineStr">
         <is>
           <t>הלכה</t>
         </is>
       </c>
-      <c r="H587" t="inlineStr"/>
-      <c r="I587" t="inlineStr">
+      <c r="H587" s="3" t="inlineStr"/>
+      <c r="I587" s="3" t="inlineStr">
         <is>
           <t>מגדולי הפוסקים שאחרי גירוש ספרד. ניצל מספינה טובעת, כיהן בדיינות במצרים ועלה בסוף ימיו לירושלים.</t>
         </is>
       </c>
-      <c r="J587" t="inlineStr"/>
+      <c r="J587" s="3" t="inlineStr"/>
     </row>
     <row r="588">
-      <c r="A588" t="inlineStr">
+      <c r="A588" s="3" t="inlineStr">
         <is>
           <t>587</t>
         </is>
       </c>
-      <c r="B588" t="inlineStr">
+      <c r="B588" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C588" t="inlineStr">
+      <c r="C588" s="3" t="inlineStr">
         <is>
           <t>רבי משה חיים אפרים מסדילקוב</t>
         </is>
       </c>
-      <c r="D588" t="inlineStr">
+      <c r="D588" s="3" t="inlineStr">
         <is>
           <t>1748–1800</t>
         </is>
       </c>
-      <c r="E588" t="inlineStr">
+      <c r="E588" s="3" t="inlineStr">
         <is>
           <t>אוקראינה</t>
         </is>
       </c>
-      <c r="F588" t="inlineStr">
+      <c r="F588" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G588" t="inlineStr">
+      <c r="G588" s="3" t="inlineStr">
         <is>
           <t>חסידות</t>
         </is>
       </c>
-      <c r="H588" t="inlineStr"/>
-      <c r="I588" t="inlineStr">
+      <c r="H588" s="3" t="inlineStr"/>
+      <c r="I588" s="3" t="inlineStr">
         <is>
           <t>נכד הבעל שם טוב ובעל 'דגל מחנה אפרים' — מן המקורות הראשונים והנאמנים לתורת הסבא הגדול.</t>
         </is>
       </c>
-      <c r="J588" t="inlineStr"/>
+      <c r="J588" s="3" t="inlineStr"/>
     </row>
     <row r="589">
-      <c r="A589" t="inlineStr">
+      <c r="A589" s="3" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="B589" t="inlineStr">
+      <c r="B589" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C589" t="inlineStr">
+      <c r="C589" s="3" t="inlineStr">
         <is>
           <t>רבי משה מקוצי (הסמ"ג)</t>
         </is>
       </c>
-      <c r="D589" t="inlineStr">
+      <c r="D589" s="3" t="inlineStr">
         <is>
           <t>1200–1260</t>
         </is>
       </c>
-      <c r="E589" t="inlineStr">
+      <c r="E589" s="3" t="inlineStr">
         <is>
           <t>צרפת</t>
         </is>
       </c>
-      <c r="F589" t="inlineStr">
+      <c r="F589" s="3" t="inlineStr">
         <is>
           <t>ראשונים</t>
         </is>
       </c>
-      <c r="G589" t="inlineStr">
+      <c r="G589" s="3" t="inlineStr">
         <is>
           <t>הלכה, דרשנות</t>
         </is>
       </c>
-      <c r="H589" t="inlineStr"/>
-      <c r="I589" t="inlineStr">
+      <c r="H589" s="3" t="inlineStr"/>
+      <c r="I589" s="3" t="inlineStr">
         <is>
           <t>מבעלי התוספות ומחבר 'ספר מצוות גדול' — הקודקס ההלכתי הגדול של יהדות צרפת. סבב בקהילות ספרד ואשכנז כמוכיח ומעורר.</t>
         </is>
       </c>
-      <c r="J589" t="inlineStr"/>
+      <c r="J589" s="3" t="inlineStr"/>
     </row>
     <row r="590">
-      <c r="A590" t="inlineStr">
+      <c r="A590" s="3" t="inlineStr">
         <is>
           <t>589</t>
         </is>
       </c>
-      <c r="B590" t="inlineStr">
+      <c r="B590" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C590" t="inlineStr">
+      <c r="C590" s="3" t="inlineStr">
         <is>
           <t>רבי נתן מברסלב (מנמירוב)</t>
         </is>
       </c>
-      <c r="D590" t="inlineStr">
+      <c r="D590" s="3" t="inlineStr">
         <is>
           <t>1780–1844</t>
         </is>
       </c>
-      <c r="E590" t="inlineStr">
+      <c r="E590" s="3" t="inlineStr">
         <is>
           <t>אוקראינה</t>
         </is>
       </c>
-      <c r="F590" t="inlineStr">
+      <c r="F590" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G590" t="inlineStr">
+      <c r="G590" s="3" t="inlineStr">
         <is>
           <t>חסידות</t>
         </is>
       </c>
-      <c r="H590" t="inlineStr"/>
-      <c r="I590" t="inlineStr">
+      <c r="H590" s="3" t="inlineStr"/>
+      <c r="I590" s="3" t="inlineStr">
         <is>
           <t>תלמידו הגדול וסופרו של רבי נחמן מברסלב. העלה על הכתב את תורותיו, ייסד את מסורת ההתבודדות והתפילה — 'ליקוטי תפילות'.</t>
         </is>
       </c>
-      <c r="J590" t="inlineStr"/>
+      <c r="J590" s="3" t="inlineStr"/>
     </row>
     <row r="591">
-      <c r="A591" t="inlineStr">
+      <c r="A591" s="3" t="inlineStr">
         <is>
           <t>590</t>
         </is>
       </c>
-      <c r="B591" t="inlineStr">
+      <c r="B591" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C591" t="inlineStr">
+      <c r="C591" s="3" t="inlineStr">
         <is>
           <t>רבי רפאל ברוך טולידאנו</t>
         </is>
       </c>
-      <c r="D591" t="inlineStr">
+      <c r="D591" s="3" t="inlineStr">
         <is>
           <t>1890–1971</t>
         </is>
       </c>
-      <c r="E591" t="inlineStr">
+      <c r="E591" s="3" t="inlineStr">
         <is>
           <t>מקנס</t>
         </is>
       </c>
-      <c r="F591" t="inlineStr">
+      <c r="F591" s="3" t="inlineStr">
         <is>
           <t>מודרני</t>
         </is>
       </c>
-      <c r="G591" t="inlineStr">
+      <c r="G591" s="3" t="inlineStr">
         <is>
           <t>הלכה, פיוט</t>
         </is>
       </c>
-      <c r="H591" t="inlineStr"/>
-      <c r="I591" t="inlineStr">
+      <c r="H591" s="3" t="inlineStr"/>
+      <c r="I591" s="3" t="inlineStr">
         <is>
           <t>ראב"ד מקנס ומחבר 'קיצור שולחן ערוך' לבני ספרד. פיוטו 'אשתחווה אפיים ארצה' מושר בכל תפוצות המזרח.</t>
         </is>
       </c>
-      <c r="J591" t="inlineStr"/>
+      <c r="J591" s="3" t="inlineStr"/>
     </row>
     <row r="592">
-      <c r="A592" t="inlineStr">
+      <c r="A592" s="3" t="inlineStr">
         <is>
           <t>591</t>
         </is>
       </c>
-      <c r="B592" t="inlineStr">
+      <c r="B592" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C592" t="inlineStr">
+      <c r="C592" s="3" t="inlineStr">
         <is>
           <t>רבן גמליאל דיבנה</t>
         </is>
       </c>
-      <c r="D592" t="inlineStr">
+      <c r="D592" s="3" t="inlineStr">
         <is>
           <t>50–118</t>
         </is>
       </c>
-      <c r="E592" t="inlineStr">
+      <c r="E592" s="3" t="inlineStr">
         <is>
           <t>יבנה</t>
         </is>
       </c>
-      <c r="F592" t="inlineStr">
+      <c r="F592" s="3" t="inlineStr">
         <is>
           <t>תנאים</t>
         </is>
       </c>
-      <c r="G592" t="inlineStr">
+      <c r="G592" s="3" t="inlineStr">
         <is>
           <t>הנהגה, הלכה</t>
         </is>
       </c>
-      <c r="H592" t="inlineStr"/>
-      <c r="I592" t="inlineStr">
+      <c r="H592" s="3" t="inlineStr"/>
+      <c r="I592" s="3" t="inlineStr">
         <is>
           <t>נשיא ישראל אחרי החורבן. ביצר את סמכות הנשיאות ואת אחדות ההלכה בדור השיקום של יבנה.</t>
         </is>
       </c>
-      <c r="J592" t="inlineStr"/>
+      <c r="J592" s="3" t="inlineStr"/>
     </row>
     <row r="593">
-      <c r="A593" t="inlineStr">
+      <c r="A593" s="3" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="B593" t="inlineStr">
+      <c r="B593" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C593" t="inlineStr">
+      <c r="C593" s="3" t="inlineStr">
         <is>
           <t>רבן יוחנן בן זכאי</t>
         </is>
       </c>
-      <c r="D593" t="inlineStr">
+      <c r="D593" s="3" t="inlineStr">
         <is>
           <t>10 לפנה״ס–74</t>
         </is>
       </c>
-      <c r="E593" t="inlineStr">
+      <c r="E593" s="3" t="inlineStr">
         <is>
           <t>יבנה</t>
         </is>
       </c>
-      <c r="F593" t="inlineStr">
+      <c r="F593" s="3" t="inlineStr">
         <is>
           <t>תנאים</t>
         </is>
       </c>
-      <c r="G593" t="inlineStr">
+      <c r="G593" s="3" t="inlineStr">
         <is>
           <t>תורה שבעל פה, הנהגה</t>
         </is>
       </c>
-      <c r="H593" t="inlineStr"/>
-      <c r="I593" t="inlineStr">
+      <c r="H593" s="3" t="inlineStr"/>
+      <c r="I593" s="3" t="inlineStr">
         <is>
           <t>מציל התורה בדור החורבן. יצא מירושלים הנצורה וביקש 'תן לי יבנה וחכמיה' — ובכך הבטיח את המשך התורה שבעל פה אחרי חורבן הבית.</t>
         </is>
       </c>
-      <c r="J593" t="inlineStr">
+      <c r="J593" s="3" t="inlineStr">
         <is>
           <t>תן לי יבנה וחכמיה</t>
         </is>
       </c>
     </row>
     <row r="594">
-      <c r="A594" t="inlineStr">
+      <c r="A594" s="3" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="B594" t="inlineStr">
+      <c r="B594" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C594" t="inlineStr">
+      <c r="C594" s="3" t="inlineStr">
         <is>
           <t>רבקה אמנו</t>
         </is>
       </c>
-      <c r="D594" t="inlineStr">
+      <c r="D594" s="3" t="inlineStr">
         <is>
           <t>1677–1556 לפנה״ס</t>
         </is>
       </c>
-      <c r="E594" t="inlineStr">
+      <c r="E594" s="3" t="inlineStr">
         <is>
           <t>חברון</t>
         </is>
       </c>
-      <c r="F594" t="inlineStr">
+      <c r="F594" s="3" t="inlineStr">
         <is>
           <t>האבות</t>
         </is>
       </c>
-      <c r="G594" t="inlineStr">
+      <c r="G594" s="3" t="inlineStr">
         <is>
           <t>אמהות האומה</t>
         </is>
       </c>
-      <c r="H594" t="inlineStr">
+      <c r="H594" s="3" t="inlineStr">
         <is>
           <t>נשים</t>
         </is>
       </c>
-      <c r="I594" t="inlineStr">
+      <c r="I594" s="3" t="inlineStr">
         <is>
           <t>השנייה שבאמהות. ראתה ברוח קודשה את ייעודם של בניה והכריעה את המשך דרך הברית — 'ורב יעבוד צעיר'.</t>
         </is>
       </c>
-      <c r="J594" t="inlineStr"/>
+      <c r="J594" s="3" t="inlineStr"/>
     </row>
     <row r="595">
-      <c r="A595" t="inlineStr">
+      <c r="A595" s="3" t="inlineStr">
         <is>
           <t>594</t>
         </is>
       </c>
-      <c r="B595" t="inlineStr">
+      <c r="B595" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C595" t="inlineStr">
+      <c r="C595" s="3" t="inlineStr">
         <is>
           <t>רש"י (רבי שלמה יצחקי)</t>
         </is>
       </c>
-      <c r="D595" t="inlineStr">
+      <c r="D595" s="3" t="inlineStr">
         <is>
           <t>1040–1105</t>
         </is>
       </c>
-      <c r="E595" t="inlineStr">
+      <c r="E595" s="3" t="inlineStr">
         <is>
           <t>טרואה</t>
         </is>
       </c>
-      <c r="F595" t="inlineStr">
+      <c r="F595" s="3" t="inlineStr">
         <is>
           <t>ראשונים</t>
         </is>
       </c>
-      <c r="G595" t="inlineStr">
+      <c r="G595" s="3" t="inlineStr">
         <is>
           <t>פרשנות המקרא, פרשנות התלמוד</t>
         </is>
       </c>
-      <c r="H595" t="inlineStr"/>
-      <c r="I595" t="inlineStr">
+      <c r="H595" s="3" t="inlineStr"/>
+      <c r="I595" s="3" t="inlineStr">
         <is>
           <t>גדול פרשני ישראל. פירושו לתורה ולתלמוד — בהיר, תמציתי וצמוד לפשט — פתח את שערי הלימוד לכל הדורות, ובלעדיו אין דף גמרא נלמד.</t>
         </is>
       </c>
-      <c r="J595" t="inlineStr">
+      <c r="J595" s="3" t="inlineStr">
         <is>
           <t>פשוטו של מקרא — פירוש שכל תלמיד יכול להיכנס בו</t>
         </is>
       </c>
     </row>
     <row r="596">
-      <c r="A596" t="inlineStr">
+      <c r="A596" s="3" t="inlineStr">
         <is>
           <t>595</t>
         </is>
       </c>
-      <c r="B596" t="inlineStr">
+      <c r="B596" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C596" t="inlineStr">
+      <c r="C596" s="3" t="inlineStr">
         <is>
           <t>שלמה המלך</t>
         </is>
       </c>
-      <c r="D596" t="inlineStr">
+      <c r="D596" s="3" t="inlineStr">
         <is>
           <t>1010–931 לפנה״ס</t>
         </is>
       </c>
-      <c r="E596" t="inlineStr">
+      <c r="E596" s="3" t="inlineStr">
         <is>
           <t>ירושלים</t>
         </is>
       </c>
-      <c r="F596" t="inlineStr">
+      <c r="F596" s="3" t="inlineStr">
         <is>
           <t>המלכים</t>
         </is>
       </c>
-      <c r="G596" t="inlineStr">
+      <c r="G596" s="3" t="inlineStr">
         <is>
           <t>חכמה, מלכות</t>
         </is>
       </c>
-      <c r="H596" t="inlineStr"/>
-      <c r="I596" t="inlineStr">
+      <c r="H596" s="3" t="inlineStr"/>
+      <c r="I596" s="3" t="inlineStr">
         <is>
           <t>החכם מכל אדם ובונה בית המקדש הראשון. חיבר את משלי, קהלת ושיר השירים.</t>
         </is>
       </c>
-      <c r="J596" t="inlineStr"/>
+      <c r="J596" s="3" t="inlineStr"/>
     </row>
     <row r="597">
-      <c r="A597" t="inlineStr">
+      <c r="A597" s="3" t="inlineStr">
         <is>
           <t>596</t>
         </is>
       </c>
-      <c r="B597" t="inlineStr">
+      <c r="B597" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C597" t="inlineStr">
+      <c r="C597" s="3" t="inlineStr">
         <is>
           <t>שמואל הנביא</t>
         </is>
       </c>
-      <c r="D597" t="inlineStr">
+      <c r="D597" s="3" t="inlineStr">
         <is>
           <t>1120–1012 לפנה״ס</t>
         </is>
       </c>
-      <c r="E597" t="inlineStr">
+      <c r="E597" s="3" t="inlineStr">
         <is>
           <t>ארץ ישראל</t>
         </is>
       </c>
-      <c r="F597" t="inlineStr">
+      <c r="F597" s="3" t="inlineStr">
         <is>
           <t>השופטים</t>
         </is>
       </c>
-      <c r="G597" t="inlineStr">
+      <c r="G597" s="3" t="inlineStr">
         <is>
           <t>נבואה, הנהגה</t>
         </is>
       </c>
-      <c r="H597" t="inlineStr"/>
-      <c r="I597" t="inlineStr">
+      <c r="H597" s="3" t="inlineStr"/>
+      <c r="I597" s="3" t="inlineStr">
         <is>
           <t>אחרון השופטים וגדול הנביאים אחרי משה. הקים את המלוכה בישראל ומשח את שאול ואת דוד.</t>
         </is>
       </c>
-      <c r="J597" t="inlineStr"/>
+      <c r="J597" s="3" t="inlineStr"/>
     </row>
     <row r="598">
-      <c r="A598" t="inlineStr">
+      <c r="A598" s="3" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="B598" t="inlineStr">
+      <c r="B598" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C598" t="inlineStr">
+      <c r="C598" s="3" t="inlineStr">
         <is>
           <t>שמואל הנגיד</t>
         </is>
       </c>
-      <c r="D598" t="inlineStr">
+      <c r="D598" s="3" t="inlineStr">
         <is>
           <t>993–1056</t>
         </is>
       </c>
-      <c r="E598" t="inlineStr">
+      <c r="E598" s="3" t="inlineStr">
         <is>
           <t>גרנדה</t>
         </is>
       </c>
-      <c r="F598" t="inlineStr">
+      <c r="F598" s="3" t="inlineStr">
         <is>
           <t>ראשונים</t>
         </is>
       </c>
-      <c r="G598" t="inlineStr">
+      <c r="G598" s="3" t="inlineStr">
         <is>
           <t>הלכה, שירה, מדינאות</t>
         </is>
       </c>
-      <c r="H598" t="inlineStr"/>
-      <c r="I598" t="inlineStr">
+      <c r="H598" s="3" t="inlineStr"/>
+      <c r="I598" s="3" t="inlineStr">
         <is>
           <t>וזיר גרנדה, מצביא, משורר ופוסק — סמל תור הזהב בספרד. 'מבוא התלמוד' שלו נלמד עד היום.</t>
         </is>
       </c>
-      <c r="J598" t="inlineStr"/>
+      <c r="J598" s="3" t="inlineStr"/>
+    </row>
+    <row r="599">
+      <c r="A599" s="3" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="B599" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C599" s="3" t="inlineStr">
+        <is>
+          <t>רבנו אשר בן יחיאל (הרא״ש)</t>
+        </is>
+      </c>
+      <c r="D599" s="3" t="inlineStr">
+        <is>
+          <t>המאות ה-13–14 (נולד סמוך ל-1250)</t>
+        </is>
+      </c>
+      <c r="E599" s="3" t="inlineStr">
+        <is>
+          <t>אשכנז; טולידו שבספרד</t>
+        </is>
+      </c>
+      <c r="F599" s="3" t="inlineStr">
+        <is>
+          <t>ראשונים</t>
+        </is>
+      </c>
+      <c r="G599" s="3" t="inlineStr">
+        <is>
+          <t>הלכה, פסיקה ופרשנות התלמוד</t>
+        </is>
+      </c>
+      <c r="H599" s="3" t="inlineStr">
+        <is>
+          <t>פסקי הרא״ש, תוספות הרא״ש, אורחות חיים, עמודי ההוראה, הגירה מאשכנז לספרד</t>
+        </is>
+      </c>
+      <c r="I599" s="3" t="inlineStr">
+        <is>
+          <t>נולד באשכנז סמוך לשנת 1250, תלמידו המובהק של המהר״ם מרוטנבורג ומנהיג יהדות גרמניה אחרי פטירת רבו בשבי. בעקבות הרדיפות עזב את גרמניה ב-1303, וב-1305 מונה לרב הקהילה ולראש הישיבה בטולידו. שם מיזג את דיאלקטיקת בעלי התוספות עם הפסיקה הספרדית, וחיבר את "פסקי הרא״ש", "תוספות הרא״ש" ו"אורחות חיים".</t>
+        </is>
+      </c>
+      <c r="J599" s="3" t="inlineStr">
+        <is>
+          <t>העברת מסורת הלימוד האשכנזית אל ספרד ויצירת סינתזה הלכתית, שהפכה אותו לאחד משלושת "עמודי ההוראה" שעליהם נשען השולחן ערוך.</t>
+        </is>
+      </c>
+      <c r="K599" s="3" t="inlineStr">
+        <is>
+          <t>המהר״ם מרוטנבורג; הרשב״א; רבי יעקב בעל הטורים; רבי יהודה בן הרא״ש; רבי יוסף קארו</t>
+        </is>
+      </c>
+      <c r="L599" s="3" t="inlineStr"/>
+    </row>
+    <row r="600">
+      <c r="A600" s="3" t="inlineStr">
+        <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="B600" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C600" s="3" t="inlineStr">
+        <is>
+          <t>רבי ישעיה הלוי הורוויץ (השל״ה הקדוש)</t>
+        </is>
+      </c>
+      <c r="D600" s="3" t="inlineStr">
+        <is>
+          <t>1558–1630</t>
+        </is>
+      </c>
+      <c r="E600" s="3" t="inlineStr">
+        <is>
+          <t>פראג ופולין; פרנקפורט; ירושלים, צפת וטבריה</t>
+        </is>
+      </c>
+      <c r="F600" s="3" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G600" s="3" t="inlineStr">
+        <is>
+          <t>הלכה, קבלה, מוסר וחינוך</t>
+        </is>
+      </c>
+      <c r="H600" s="3" t="inlineStr">
+        <is>
+          <t>שני לוחות הברית, שער השמים, עלייה לארץ ישראל, קבלת האר״י, פראג</t>
+        </is>
+      </c>
+      <c r="I600" s="3" t="inlineStr">
+        <is>
+          <t>נולד בפראג בשנת 1558 וכיהן ברבנות דובנא, אוסטראה, פוזן, קראקא, וינה ופרנקפורט; בגירוש פרנקפורט (1614–1615) יצא לגלות יחד עם קהילתו. בשנת 1621 עלה לארץ ישראל, שימש רבה של הקהילה האשכנזית בירושלים ונאסר בידי המושל אבן פרוך, ונפטר בטבריה בשנת 1630.</t>
+        </is>
+      </c>
+      <c r="J600" s="3" t="inlineStr">
+        <is>
+          <t>"שני לוחות הברית" מאחד הלכה, קבלה ומוסר לאנציקלופדיה תורנית אחת, המארגנת את חיי היהודי סביב קדושה, כוונה וחינוך הדורות הבאים.</t>
+        </is>
+      </c>
+      <c r="K600" s="3" t="inlineStr">
+        <is>
+          <t>הרמ״א; המהרש״ל; המהר״ם מלובלין; המהר״ל מפראג; רבי חיים ויטאל</t>
+        </is>
+      </c>
+      <c r="L600" s="3" t="inlineStr"/>
+    </row>
+    <row r="601">
+      <c r="A601" s="3" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="B601" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C601" s="3" t="inlineStr">
+        <is>
+          <t>רבי אברהם בן הרמב״ם</t>
+        </is>
+      </c>
+      <c r="D601" s="3" t="inlineStr">
+        <is>
+          <t>1186–1237</t>
+        </is>
+      </c>
+      <c r="E601" s="3" t="inlineStr">
+        <is>
+          <t>פוסטאט, מצרים</t>
+        </is>
+      </c>
+      <c r="F601" s="3" t="inlineStr">
+        <is>
+          <t>ראשונים</t>
+        </is>
+      </c>
+      <c r="G601" s="3" t="inlineStr">
+        <is>
+          <t>הלכה, הנהגה ומחשבה מיסטית</t>
+        </is>
+      </c>
+      <c r="H601" s="3" t="inlineStr">
+        <is>
+          <t>נגידות, המספיק לעובדי השם, חסידי מצרים, ברכת אברהם, מורשת הרמב״ם</t>
+        </is>
+      </c>
+      <c r="I601" s="3" t="inlineStr">
+        <is>
+          <t>בנו יחידו של הרמב״ם, נולד בפוסטאט ב-1186 ומונה לנגיד יהודי מצרים, סוריה וארץ ישראל בהיותו בן שמונה עשרה, לאחר פטירת אביו ב-1204. הנהיג את הקהילה שלושים ושלוש שנים, הגן על משנת אביו בפולמוסים, וחיבר את "המספיק לעובדי השם" ואת התשובות שנאספו ב"ברכת אברהם". נפטר בשנת 1237 בגיל 51.</t>
+        </is>
+      </c>
+      <c r="J601" s="3" t="inlineStr">
+        <is>
+          <t>"חסידות רציונלית": שילוב הפילוסופיה המימונית עם דרכי פרישות, כוונה ודבקות, מתוך עמדה שדקדוק המצוות והדבקות המיסטית משלימים זה את זה.</t>
+        </is>
+      </c>
+      <c r="K601" s="3" t="inlineStr">
+        <is>
+          <t>הרמב״ם; רבי עובדיה בן אברהם; חסידי מצרים</t>
+        </is>
+      </c>
+      <c r="L601" s="3" t="inlineStr"/>
+    </row>
+    <row r="602">
+      <c r="A602" s="3" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="B602" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C602" s="3" t="inlineStr">
+        <is>
+          <t>רבנו חזקיה די סילוה (פרי חדש)</t>
+        </is>
+      </c>
+      <c r="D602" s="3" t="inlineStr">
+        <is>
+          <t>המאה ה-17 (נולד בליוורנו 1656; נפטר בן 39)</t>
+        </is>
+      </c>
+      <c r="E602" s="3" t="inlineStr">
+        <is>
+          <t>ליוורנו; ירושלים; אמסטרדם</t>
+        </is>
+      </c>
+      <c r="F602" s="3" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G602" s="3" t="inlineStr">
+        <is>
+          <t>הלכה ופסיקה; בניין מוסדות התורה בירושלים</t>
+        </is>
+      </c>
+      <c r="H602" s="3" t="inlineStr">
+        <is>
+          <t>פרי חדש, ישיבת בית יעקב פירירא, שד״רות, פולמוס החרם, ירושלים העות׳מאנית</t>
+        </is>
+      </c>
+      <c r="I602" s="3" t="inlineStr">
+        <is>
+          <t>נולד בליוורנו בשנת 1656 ועלה לירושלים, שם נמנה עם ישיבת "בית יעקב" ופעל להקמת ישיבת בית יעקב (פירירא) בסיוע הגביר יעקב פירירא. בשנת 1688 יצא בשליחות דרבנן לאירופה והדפיס את ספרו "פרי חדש", שעורר פולמוס חריף וחרם במצרים. נפטר בכ״ח בכסלו והוא בן 39 בלבד.</t>
+        </is>
+      </c>
+      <c r="J602" s="3" t="inlineStr">
+        <is>
+          <t>תעוזה הלכתית: חזרה לבירור הסוגיה מן המקור וביקורת גלויה על פסקי הקודמים, לצד ביסוס ירושלים כמרכז תורה עולמי.</t>
+        </is>
+      </c>
+      <c r="K602" s="3" t="inlineStr">
+        <is>
+          <t>רבי שמואל קוסטא; המהר״ם גאלנטי; יעקב פירירא</t>
+        </is>
+      </c>
+      <c r="L602" s="3" t="inlineStr"/>
+    </row>
+    <row r="603">
+      <c r="A603" s="3" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="B603" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C603" s="3" t="inlineStr">
+        <is>
+          <t>רבי יצחק בן אבא מרי (בעל העיטור)</t>
+        </is>
+      </c>
+      <c r="D603" s="3" t="inlineStr">
+        <is>
+          <t>1122–1193</t>
+        </is>
+      </c>
+      <c r="E603" s="3" t="inlineStr">
+        <is>
+          <t>מרסיי, פרובנס</t>
+        </is>
+      </c>
+      <c r="F603" s="3" t="inlineStr">
+        <is>
+          <t>ראשונים</t>
+        </is>
+      </c>
+      <c r="G603" s="3" t="inlineStr">
+        <is>
+          <t>הלכה, פסיקה וארגון הידע ההלכתי</t>
+        </is>
+      </c>
+      <c r="H603" s="3" t="inlineStr">
+        <is>
+          <t>ספר העיטור, פרובנס, תורת הגאונים, דיני שטרות, סינתזה הלכתית</t>
+        </is>
+      </c>
+      <c r="I603" s="3" t="inlineStr">
+        <is>
+          <t>נולד בשנת 1122 ופעל במרסיי שבפרובנס עד פטירתו בשנת 1193. חיבורו "ספר העיטור" מארגן את הידע ההלכתי של דורו במבנה שיטתי וחדשני, ומשלב נאמנות לתורת הגאונים עם כלים פרשניים מקוריים ונועזים.</t>
+        </is>
+      </c>
+      <c r="J603" s="3" t="inlineStr">
+        <is>
+          <t>ארכיטקטורה הלכתית: ארגון ההלכה כמערכת משפטית שיטתית, המגשרת בין למדנות ספרד המוסלמית לבין ישיבות צפון צרפת ואשכנז.</t>
+        </is>
+      </c>
+      <c r="K603" s="3" t="inlineStr">
+        <is>
+          <t>תורת הגאונים; חכמי פרובנס; בעלי התוספות</t>
+        </is>
+      </c>
+      <c r="L603" s="3" t="inlineStr"/>
+    </row>
+    <row r="604">
+      <c r="A604" s="3" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="B604" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C604" s="3" t="inlineStr">
+        <is>
+          <t>רבי יעקב אבן חביב (עין יעקב)</t>
+        </is>
+      </c>
+      <c r="D604" s="3" t="inlineStr">
+        <is>
+          <t>אמצע המאה ה-15 – 1516</t>
+        </is>
+      </c>
+      <c r="E604" s="3" t="inlineStr">
+        <is>
+          <t>זמורה שבקסטיליה, ספרד; פורטוגל; סלוניקי</t>
+        </is>
+      </c>
+      <c r="F604" s="3" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G604" s="3" t="inlineStr">
+        <is>
+          <t>אגדה, הלכה ומנהיגות קהילת המגורשים</t>
+        </is>
+      </c>
+      <c r="H604" s="3" t="inlineStr">
+        <is>
+          <t>עין יעקב, גירוש ספרד, אגדות התלמוד, סלוניקי, אנוסים</t>
+        </is>
+      </c>
+      <c r="I604" s="3" t="inlineStr">
+        <is>
+          <t>ראש ישיבה נערץ בקסטיליה שגורש מספרד בשנת 1492, נמלט מפורטוגל אחרי גזירת ההמרה של 1497 והנהיג את קהילת המגורשים בסלוניקי. חיבר את "עין יעקב", כינוס אגדות התלמוד עם פירוש, ופירוש ל"ארבעה טורים" שעמד לפני רבי יוסף קארו בכתיבת "בית יוסף". נפטר בסלוניקי בשנת 1516, ובנו המהרלב״ח השלים את מפעלו.</t>
+        </is>
+      </c>
+      <c r="J604" s="3" t="inlineStr">
+        <is>
+          <t>שיקום האמונה אחרי החורבן דרך אגדות חז״ל: האגדה כמסד רוחני ומקור תקווה לדור מגורשים שאיבד את עולמו הפיזי.</t>
+        </is>
+      </c>
+      <c r="K604" s="3" t="inlineStr">
+        <is>
+          <t>רבי לוי אבן חביב (המהרלב״ח); רבי יצחק אבוהב; רבי יוסף קארו</t>
+        </is>
+      </c>
+      <c r="L604" s="3" t="inlineStr"/>
+    </row>
+    <row r="605">
+      <c r="A605" s="3" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="B605" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C605" s="3" t="inlineStr">
+        <is>
+          <t>רבי יעקב בן יקר</t>
+        </is>
+      </c>
+      <c r="D605" s="3" t="inlineStr">
+        <is>
+          <t>בערך 990–1064</t>
+        </is>
+      </c>
+      <c r="E605" s="3" t="inlineStr">
+        <is>
+          <t>מגנצא (מיינץ) וורמייזא, אשכנז</t>
+        </is>
+      </c>
+      <c r="F605" s="3" t="inlineStr">
+        <is>
+          <t>ראשונים</t>
+        </is>
+      </c>
+      <c r="G605" s="3" t="inlineStr">
+        <is>
+          <t>תלמוד, מסורת הנוסח והנהגת ישיבות אשכנז</t>
+        </is>
+      </c>
+      <c r="H605" s="3" t="inlineStr">
+        <is>
+          <t>רבו של רש״י, מגנצא, רבנו גרשום, הגהת נוסח התלמוד, ענווה</t>
+        </is>
+      </c>
+      <c r="I605" s="3" t="inlineStr">
+        <is>
+          <t>תלמידו של רבנו גרשום מאור הגולה וממשיך דרכו בהנהגת הישיבה במגנצא לאחר פטירתו ב-1028, ורבו המובהק של רש״י. נולד בערך בשנת 990 ונפטר בשנת 1064, ונקבר בבית העלמין העתיק של מגנצא.</t>
+        </is>
+      </c>
+      <c r="J605" s="3" t="inlineStr">
+        <is>
+          <t>העמדת מסורת הלימוד והגהת נוסח התלמוד של אשכנז הקדומה — מלאכה שהגיעה לשיאה אצל תלמידו רש״י.</t>
+        </is>
+      </c>
+      <c r="K605" s="3" t="inlineStr">
+        <is>
+          <t>רבנו גרשום מאור הגולה; רש״י; רבי אליעזר הגדול</t>
+        </is>
+      </c>
+      <c r="L605" s="3" t="inlineStr"/>
+    </row>
+    <row r="606">
+      <c r="A606" s="3" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="B606" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C606" s="3" t="inlineStr">
+        <is>
+          <t>רבי יוסי בן חלפתא</t>
+        </is>
+      </c>
+      <c r="D606" s="3" t="inlineStr">
+        <is>
+          <t>דור רביעי לתנאים; לאחר מרד בר כוכבא (המאה ה-2 לספירה)</t>
+        </is>
+      </c>
+      <c r="E606" s="3" t="inlineStr">
+        <is>
+          <t>ציפורי והגליל, ארץ ישראל</t>
+        </is>
+      </c>
+      <c r="F606" s="3" t="inlineStr">
+        <is>
+          <t>תנאים</t>
+        </is>
+      </c>
+      <c r="G606" s="3" t="inlineStr">
+        <is>
+          <t>הלכה, אגדה וכרונולוגיה</t>
+        </is>
+      </c>
+      <c r="H606" s="3" t="inlineStr">
+        <is>
+          <t>נימוקו עמו, סדר עולם רבה, ציפורי, דור אושא, עיבוד עורות</t>
+        </is>
+      </c>
+      <c r="I606" s="3" t="inlineStr">
+        <is>
+          <t>תנא מן הדור הרביעי, נולד בציפורי לבנו של רבי חלפתא ולמד אצל רבו המובהק רבי עקיבא. תלמידו איסי בן יהודה טבע עליו את הכלל "רבי יוסי – נימוקו עמו", ופסקיו המנומקים הפכו מכריעים כמעט בכל מחלוקת. חיבר את "סדר עולם", הכרוניקה העברית השיטתית הראשונה של הכרונולוגיה המקראית.</t>
+        </is>
+      </c>
+      <c r="J606" s="3" t="inlineStr">
+        <is>
+          <t>הנמקה כמקור סמכות: פסיקה ברורה ומנומקת ככלי לאיחוי עם מפולג אחרי החורבן, וסדר כרונולוגי כעוגן לזיכרון הלאומי.</t>
+        </is>
+      </c>
+      <c r="K606" s="3" t="inlineStr">
+        <is>
+          <t>רבי חלפתא; רבי עקיבא; איסי בן יהודה</t>
+        </is>
+      </c>
+      <c r="L606" s="3" t="inlineStr"/>
+    </row>
+    <row r="607">
+      <c r="A607" s="3" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="B607" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C607" s="3" t="inlineStr">
+        <is>
+          <t>מרדכי היהודי</t>
+        </is>
+      </c>
+      <c r="D607" s="3" t="inlineStr">
+        <is>
+          <t>ימי פרס ותחילת בית שני</t>
+        </is>
+      </c>
+      <c r="E607" s="3" t="inlineStr">
+        <is>
+          <t>שושן הבירה, פרס; ירושלים</t>
+        </is>
+      </c>
+      <c r="F607" s="3" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="G607" s="3" t="inlineStr">
+        <is>
+          <t>מנהיגות, הלכה וגאולה</t>
+        </is>
+      </c>
+      <c r="H607" s="3" t="inlineStr">
+        <is>
+          <t>מגילת אסתר, כנסת הגדולה, סנהדרין, מרדכי בלשן, שיבת ציון</t>
+        </is>
+      </c>
+      <c r="I607" s="3" t="inlineStr">
+        <is>
+          <t>מנהיג יהודי פרס בימי אחשוורוש, חבר בסנהדרין ומאנשי כנסת הגדולה, המכונה "מרדכי בלשן" על שום שליטתו בלשונות — שבזכותה חשף את מזימת בגתן ותרש. פעל לביצור היישוב היהודי בגולה ובירושלים כאחד, ודמותו נדרשת כגשר בין תקופת הנבואה לבין ראשית עידן ההלכה והנהגת החכמים.</t>
+        </is>
+      </c>
+      <c r="J607" s="3" t="inlineStr">
+        <is>
+          <t>מנהיגות המשלבת דבקות דתית בלתי מתפשרת עם תחכום מדיני: תרגום רצון ה' לשפות המציאות הפוליטית מבלי לאבד את הגרעין המקודש.</t>
+        </is>
+      </c>
+      <c r="K607" s="3" t="inlineStr">
+        <is>
+          <t>אסתר המלכה; אנשי כנסת הגדולה; המן האגגי</t>
+        </is>
+      </c>
+      <c r="L607" s="3" t="inlineStr"/>
+    </row>
+    <row r="608">
+      <c r="A608" s="3" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="B608" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C608" s="3" t="inlineStr">
+        <is>
+          <t>יצחק שמואל רג׳יו (יש״ר מגוריציה)</t>
+        </is>
+      </c>
+      <c r="D608" s="3" t="inlineStr">
+        <is>
+          <t>1784–1855</t>
+        </is>
+      </c>
+      <c r="E608" s="3" t="inlineStr">
+        <is>
+          <t>גוריציה ופדובה, איטליה והאימפריה האוסטרית</t>
+        </is>
+      </c>
+      <c r="F608" s="3" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="G608" s="3" t="inlineStr">
+        <is>
+          <t>הגות, חינוך רבני ופרשנות המקרא</t>
+        </is>
+      </c>
+      <c r="H608" s="3" t="inlineStr">
+        <is>
+          <t>בית המדרש לרבנים בפדובה, התורה והפילוסופיה, השכלה איטלקית, ביקורת הקבלה, שד״ל</t>
+        </is>
+      </c>
+      <c r="I608" s="3" t="inlineStr">
+        <is>
+          <t>נולד בגוריציה בשנת 1784 ולמד תלמוד ודקדוק מאביו לצד מדעים ולשונות אירופה. יזם והקים את בית המדרש לרבנים בפדובה, שנפתח ב-1829 והיה הסמינר הרבני המודרני הראשון באירופה, ובו לימד שד״ל. בספרו "התורה והפילוסופיה" ביקש לפייס בין תבונה ומדע לבין אמונה, ובכתביו המאוחרים ביקר את הקבלה ואת הסמכות הרבנית המקובלת.</t>
+        </is>
+      </c>
+      <c r="J608" s="3" t="inlineStr">
+        <is>
+          <t>פיוס בין תבונה לאמונה: הנהגה רבנית מחייבת גם ידע תורני וגם השכלה כללית, ומכאן הצורך בהכשרה רבנית מודרנית ומוסדית.</t>
+        </is>
+      </c>
+      <c r="K608" s="3" t="inlineStr">
+        <is>
+          <t>משה מנדלסון; נפתלי הרץ ויזל; שד״ל (שמואל דוד לוצאטו); ליליו דלה טורה</t>
+        </is>
+      </c>
+      <c r="L608" s="3" t="inlineStr"/>
+    </row>
+    <row r="609">
+      <c r="A609" s="3" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="B609" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C609" s="3" t="inlineStr">
+        <is>
+          <t>רבי יוסף דב הלוי סולובייצ׳יק (הגרי״ד)</t>
+        </is>
+      </c>
+      <c r="D609" s="3" t="inlineStr">
+        <is>
+          <t>1903–1993</t>
+        </is>
+      </c>
+      <c r="E609" s="3" t="inlineStr">
+        <is>
+          <t>בריסק וליטא; ברלין; בוסטון וניו יורק</t>
+        </is>
+      </c>
+      <c r="F609" s="3" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="G609" s="3" t="inlineStr">
+        <is>
+          <t>תלמוד בשיטת בריסק, פילוסופיה והנהגת האורתודוקסיה המודרנית</t>
+        </is>
+      </c>
+      <c r="H609" s="3" t="inlineStr">
+        <is>
+          <t>שיטת בריסק, הגרי״ד, ישיבה יוניברסיטי, אורתודוקסיה מודרנית, בוסטון, גברא וחפצא</t>
+        </is>
+      </c>
+      <c r="I609" s="3" t="inlineStr">
+        <is>
+          <t>נכדו של רבי חיים סולובייצ׳יק וממשיך שיטת בריסק האנליטית, הנקרא על שם זקנו רבי יוסף דב הלוי בעל "בית הלוי" (1820–1892). למד בברלין, ובשנת 1932 היגר לארצות הברית; שם הנהיג את הקהילה בבוסטון ועמד בראש ההוראה בישיבה יוניברסיטי במשך למעלה מארבעה עשורים, כארכיטקט הרוחני של האורתודוקסיה המודרנית.</t>
+        </is>
+      </c>
+      <c r="J609" s="3" t="inlineStr">
+        <is>
+          <t>חיבור בין הדיוק המושגי של שיטת בריסק לבין הפילוסופיה המערבית: התורה כמערכת לוגית אוטונומית שדרך קטגוריותיה נקראת המציאות המודרנית.</t>
+        </is>
+      </c>
+      <c r="K609" s="3" t="inlineStr">
+        <is>
+          <t>רבי חיים סולובייצ׳יק; בית הלוי; רבי חיים מוולוז׳ין</t>
+        </is>
+      </c>
+      <c r="L609" s="3" t="inlineStr"/>
+    </row>
+    <row r="610">
+      <c r="A610" s="3" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="B610" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C610" s="3" t="inlineStr">
+        <is>
+          <t>רבי ירמיהו חחיאשוילי</t>
+        </is>
+      </c>
+      <c r="D610" s="3" t="inlineStr">
+        <is>
+          <t>המאה ה-20</t>
+        </is>
+      </c>
+      <c r="E610" s="3" t="inlineStr">
+        <is>
+          <t>כותאיסי, גאורגיה; אשדוד, ישראל</t>
+        </is>
+      </c>
+      <c r="F610" s="3" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="G610" s="3" t="inlineStr">
+        <is>
+          <t>רבנות, הלכה ומנהיגות קהילתית</t>
+        </is>
+      </c>
+      <c r="H610" s="3" t="inlineStr">
+        <is>
+          <t>יהדות גאורגיה, כותאיסי, מסורת גאורגית, שלטון סובייטי, אשדוד</t>
+        </is>
+      </c>
+      <c r="I610" s="3" t="inlineStr">
+        <is>
+          <t>בנו וממשיך דרכו של חכם חיים אליאשווילי (חחיאשוילי), רבה של כותאיסי — "ירושלים של גאורגיה" — שהוביל בשנת 1924 את המאבק להחזרת בתי הכנסת מידי השלטון הסובייטי. רבי ירמיהו הנהיג את הקהילה תחת המשטר הקומוניסטי, עלה לישראל והיה למגדלור רוחני ליוצאי גאורגיה באשדוד, תוך שמירה קפדנית על המנהג הגאורגי.</t>
+        </is>
+      </c>
+      <c r="J610" s="3" t="inlineStr">
+        <is>
+          <t>רבנות אקטיביסטית: הרב כמיופה כוח הציבור, האחראי לא רק להוראה אלא גם למאבק המשפטי והציבורי על מוסדות הקהילה ובתי הכנסת.</t>
+        </is>
+      </c>
+      <c r="K610" s="3" t="inlineStr">
+        <is>
+          <t>חכם חיים אליאשווילי (חחיאשוילי); יהדות גאורגיה</t>
+        </is>
+      </c>
+      <c r="L610" s="3" t="inlineStr"/>
+    </row>
+    <row r="611">
+      <c r="A611" s="3" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="B611" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C611" s="3" t="inlineStr">
+        <is>
+          <t>הרבנית חיה מושקא שניאורסון</t>
+        </is>
+      </c>
+      <c r="D611" s="3" t="inlineStr">
+        <is>
+          <t>1901–1988</t>
+        </is>
+      </c>
+      <c r="E611" s="3" t="inlineStr">
+        <is>
+          <t>ליובאוויטש ורוסטוב, רוסיה; ניו יורק</t>
+        </is>
+      </c>
+      <c r="F611" s="3" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="G611" s="3" t="inlineStr">
+        <is>
+          <t>מנהיגות רוחנית, חסד וחינוך</t>
+        </is>
+      </c>
+      <c r="H611" s="3" t="inlineStr">
+        <is>
+          <t>חב״ד, ליובאוויטש, משפט הספרים, פעילות מחתרתית, צניעות, כ״ב שבט</t>
+        </is>
+      </c>
+      <c r="I611" s="3" t="inlineStr">
+        <is>
+          <t>בתו של האדמו״ר רבי יוסף יצחק שניאורסון ואשתו של הרבי מליובאוויטש. נולדה בשנת 1901 סמוך לליובאוויטש, נטלה חלק בפעילות המחתרתית לשימור היהדות בברית המועצות ובמאמצים סביב מאסר אביה ב-1927, ונמלטה עם בעלה מאירופה הכבושה עד הגעתם לניו יורק ב-1941. עדותה במשפט הספרים — "אבי והספרים שייכים לחסידים" — הכריעה את הדין. הסתלקה בכ״ב בשבט תשמ״ח (1988).</t>
+        </is>
+      </c>
+      <c r="J611" s="3" t="inlineStr">
+        <is>
+          <t>צניעות קיצונית והסתרה לצד חוסן רוחני ואחריות ציבורית: הצדיק ונכסיו שייכים לכלל החסידים ולא לפרט.</t>
+        </is>
+      </c>
+      <c r="K611" s="3" t="inlineStr">
+        <is>
+          <t>הרב יוסף יצחק שניאורסון (הריי״צ); הרבי מליובאוויטש; הרבנית נחמה דינה</t>
+        </is>
+      </c>
+      <c r="L611" s="3" t="inlineStr"/>
+    </row>
+    <row r="612">
+      <c r="A612" s="3" t="inlineStr">
+        <is>
+          <t>611</t>
+        </is>
+      </c>
+      <c r="B612" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C612" s="3" t="inlineStr">
+        <is>
+          <t>גאולה כהן</t>
+        </is>
+      </c>
+      <c r="D612" s="3" t="inlineStr">
+        <is>
+          <t>1925–2019</t>
+        </is>
+      </c>
+      <c r="E612" s="3" t="inlineStr">
+        <is>
+          <t>תל אביב וירושלים, ארץ ישראל</t>
+        </is>
+      </c>
+      <c r="F612" s="3" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="G612" s="3" t="inlineStr">
+        <is>
+          <t>מנהיגות לאומית, פוליטיקה ומורשת</t>
+        </is>
+      </c>
+      <c r="H612" s="3" t="inlineStr">
+        <is>
+          <t>לח״י, תנועת התחיה, המדרשה הלאומית, בית מורשת אורי צבי גרינברג, פרס ישראל</t>
+        </is>
+      </c>
+      <c r="I612" s="3" t="inlineStr">
+        <is>
+          <t>נולדה בתל אביב בשנת 1925 והצטרפה בשלהי 1943 למחתרת לח״י, שבה הייתה "הקול של הלח״י" בשידורי המחתרת. כיהנה בכנסת תשע עשרה שנים ברציפות עד 1992, פרשה מהליכוד ב-1978 בעקבות הסכמי קמפ דיוויד, וייסדה עם יובל נאמן את תנועת "התחיה". הקימה את המדרשה הלאומית ואת בית מורשת אורי צבי גרינברג, זכתה בפרס ישראל ב-2003 ונפטרה ב-2019.</t>
+        </is>
+      </c>
+      <c r="J612" s="3" t="inlineStr">
+        <is>
+          <t>הפיכת המילה המשודרת והכתובה לכלי מאבק לאומי, וחיבור בין מורשת המחתרות לבין מפעל ההתיישבות והחינוך הציוני.</t>
+        </is>
+      </c>
+      <c r="K612" s="3" t="inlineStr">
+        <is>
+          <t>יובל נאמן; הרב צבי יהודה קוק; אורי צבי גרינברג</t>
+        </is>
+      </c>
+      <c r="L612" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
